--- a/assets/contents.xlsx
+++ b/assets/contents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Courses\duyiFe\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0BF42A-F3A3-4B3A-86FC-0F9FC0D5D20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E56CDD-B56B-4498-AE0C-B4D444E9530E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4965" yWindow="2085" windowWidth="21600" windowHeight="11820" tabRatio="722" firstSheet="18" activeTab="18" xr2:uid="{977D219B-3D5A-4B74-BC43-A61DD328A31A}"/>
+    <workbookView xWindow="2040" yWindow="2820" windowWidth="21600" windowHeight="11820" tabRatio="722" firstSheet="18" activeTab="18" xr2:uid="{977D219B-3D5A-4B74-BC43-A61DD328A31A}"/>
   </bookViews>
   <sheets>
     <sheet name="1HTML_scratch" sheetId="9" r:id="rId1"/>
@@ -3953,7 +3953,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4219,6 +4219,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9140,56 +9143,56 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="A2" s="57" t="s">
         <v>544</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="57">
         <v>19</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="57">
         <v>15</v>
       </c>
-      <c r="D2" s="88">
+      <c r="D2" s="89">
         <f>B2/1440+C2/86400</f>
         <v>1.3368055555555555E-2</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="45">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="57" t="s">
         <v>545</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="57">
         <v>23</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="57">
         <v>29</v>
       </c>
-      <c r="D3" s="88">
+      <c r="D3" s="89">
         <f>B3/1440+C3/86400</f>
         <v>1.6307870370370368E-2</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="45">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="57" t="s">
         <v>546</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="57">
         <v>24</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="57">
         <v>31</v>
       </c>
-      <c r="D4" s="88">
+      <c r="D4" s="89">
         <f>B4/1440+C4/86400</f>
         <v>1.7025462962962964E-2</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="45">
         <v>2</v>
       </c>
     </row>
@@ -9228,7 +9231,7 @@
         <v>39</v>
       </c>
       <c r="D7" s="88">
-        <f>B7/1440+C7/86400</f>
+        <f t="shared" ref="D7:D21" si="0">B7/1440+C7/86400</f>
         <v>1.0868055555555554E-2</v>
       </c>
       <c r="E7" s="25">
@@ -9246,7 +9249,7 @@
         <v>53</v>
       </c>
       <c r="D8" s="88">
-        <f>B8/1440+C8/86400</f>
+        <f t="shared" si="0"/>
         <v>4.0891203703703707E-2</v>
       </c>
       <c r="E8" s="25">
@@ -9264,7 +9267,7 @@
         <v>33</v>
       </c>
       <c r="D9" s="88">
-        <f>B9/1440+C9/86400</f>
+        <f t="shared" si="0"/>
         <v>1.21875E-2</v>
       </c>
       <c r="E9" s="25">
@@ -9282,7 +9285,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="88">
-        <f>B10/1440+C10/86400</f>
+        <f t="shared" si="0"/>
         <v>4.3611111111111107E-2</v>
       </c>
       <c r="E10" s="25">
@@ -9300,7 +9303,7 @@
         <v>58</v>
       </c>
       <c r="D11" s="88">
-        <f>B11/1440+C11/86400</f>
+        <f t="shared" si="0"/>
         <v>3.2615740740740737E-2</v>
       </c>
       <c r="E11" s="25">
@@ -9318,7 +9321,7 @@
         <v>58</v>
       </c>
       <c r="D12" s="88">
-        <f>B12/1440+C12/86400</f>
+        <f t="shared" si="0"/>
         <v>4.0949074074074075E-2</v>
       </c>
       <c r="E12" s="25">
@@ -9336,7 +9339,7 @@
         <v>28</v>
       </c>
       <c r="D13" s="88">
-        <f>B13/1440+C13/86400</f>
+        <f t="shared" si="0"/>
         <v>2.810185185185185E-2</v>
       </c>
       <c r="E13" s="25">
@@ -9354,7 +9357,7 @@
         <v>4</v>
       </c>
       <c r="D14" s="88">
-        <f>B14/1440+C14/86400</f>
+        <f t="shared" si="0"/>
         <v>3.9629629629629626E-2</v>
       </c>
       <c r="E14" s="25">
@@ -9372,7 +9375,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="88">
-        <f>B15/1440+C15/86400</f>
+        <f t="shared" si="0"/>
         <v>5.4537037037037037E-2</v>
       </c>
       <c r="E15" s="25">
@@ -9390,7 +9393,7 @@
         <v>35</v>
       </c>
       <c r="D16" s="88">
-        <f>B16/1440+C16/86400</f>
+        <f t="shared" si="0"/>
         <v>3.0266203703703705E-2</v>
       </c>
       <c r="E16" s="25">
@@ -9408,7 +9411,7 @@
         <v>53</v>
       </c>
       <c r="D17" s="88">
-        <f>B17/1440+C17/86400</f>
+        <f t="shared" si="0"/>
         <v>5.5474537037037037E-2</v>
       </c>
       <c r="E17" s="25">
@@ -9426,7 +9429,7 @@
         <v>47</v>
       </c>
       <c r="D18" s="88">
-        <f>B18/1440+C18/86400</f>
+        <f t="shared" si="0"/>
         <v>1.0960648148148148E-2</v>
       </c>
       <c r="E18" s="25">
@@ -9444,7 +9447,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="88">
-        <f>B19/1440+C19/86400</f>
+        <f t="shared" si="0"/>
         <v>5.2152777777777777E-2</v>
       </c>
       <c r="E19" s="25">
@@ -9462,7 +9465,7 @@
         <v>46</v>
       </c>
       <c r="D20" s="88">
-        <f>B20/1440+C20/86400</f>
+        <f t="shared" si="0"/>
         <v>1.0254629629629629E-2</v>
       </c>
       <c r="E20" s="25">
@@ -9480,7 +9483,7 @@
         <v>52</v>
       </c>
       <c r="D21" s="88">
-        <f>B21/1440+C21/86400</f>
+        <f t="shared" si="0"/>
         <v>2.4907407407407409E-2</v>
       </c>
       <c r="E21" s="25">
@@ -9504,7 +9507,7 @@
         <v>28</v>
       </c>
       <c r="D23" s="88">
-        <f>B23/1440+C23/86400</f>
+        <f t="shared" ref="D23:D33" si="1">B23/1440+C23/86400</f>
         <v>5.8796296296296296E-3</v>
       </c>
       <c r="E23" s="25">
@@ -9522,7 +9525,7 @@
         <v>10</v>
       </c>
       <c r="D24" s="88">
-        <f>B24/1440+C24/86400</f>
+        <f t="shared" si="1"/>
         <v>1.1921296296296296E-2</v>
       </c>
       <c r="E24" s="25">
@@ -9540,7 +9543,7 @@
         <v>25</v>
       </c>
       <c r="D25" s="88">
-        <f>B25/1440+C25/86400</f>
+        <f t="shared" si="1"/>
         <v>3.7615740740740739E-3</v>
       </c>
       <c r="E25" s="25">
@@ -9558,7 +9561,7 @@
         <v>16</v>
       </c>
       <c r="D26" s="88">
-        <f>B26/1440+C26/86400</f>
+        <f t="shared" si="1"/>
         <v>9.2129629629629627E-3</v>
       </c>
       <c r="E26" s="25">
@@ -9576,7 +9579,7 @@
         <v>23</v>
       </c>
       <c r="D27" s="88">
-        <f>B27/1440+C27/86400</f>
+        <f t="shared" si="1"/>
         <v>1.6238425925925924E-2</v>
       </c>
       <c r="E27" s="25">
@@ -9594,7 +9597,7 @@
         <v>57</v>
       </c>
       <c r="D28" s="88">
-        <f>B28/1440+C28/86400</f>
+        <f t="shared" si="1"/>
         <v>6.2152777777777779E-3</v>
       </c>
       <c r="E28" s="25">
@@ -9612,7 +9615,7 @@
         <v>46</v>
       </c>
       <c r="D29" s="88">
-        <f>B29/1440+C29/86400</f>
+        <f t="shared" si="1"/>
         <v>1.3032407407407407E-2</v>
       </c>
       <c r="E29" s="25">
@@ -9630,7 +9633,7 @@
         <v>55</v>
       </c>
       <c r="D30" s="88">
-        <f>B30/1440+C30/86400</f>
+        <f t="shared" si="1"/>
         <v>4.1087962962962962E-3</v>
       </c>
       <c r="E30" s="25">
@@ -9648,7 +9651,7 @@
         <v>21</v>
       </c>
       <c r="D31" s="88">
-        <f>B31/1440+C31/86400</f>
+        <f t="shared" si="1"/>
         <v>3.0208333333333333E-3</v>
       </c>
       <c r="E31" s="25">
@@ -9666,7 +9669,7 @@
         <v>55</v>
       </c>
       <c r="D32" s="88">
-        <f>B32/1440+C32/86400</f>
+        <f t="shared" si="1"/>
         <v>1.5914351851851853E-2</v>
       </c>
       <c r="E32" s="25">
@@ -9684,7 +9687,7 @@
         <v>39</v>
       </c>
       <c r="D33" s="88">
-        <f>B33/1440+C33/86400</f>
+        <f t="shared" si="1"/>
         <v>7.3958333333333333E-3</v>
       </c>
       <c r="E33" s="25">

--- a/assets/contents.xlsx
+++ b/assets/contents.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Courses\duyiFe\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E56CDD-B56B-4498-AE0C-B4D444E9530E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247F28C5-7872-4569-826A-4FEAF4C2455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="2820" windowWidth="21600" windowHeight="11820" tabRatio="722" firstSheet="18" activeTab="18" xr2:uid="{977D219B-3D5A-4B74-BC43-A61DD328A31A}"/>
+    <workbookView xWindow="1845" yWindow="1860" windowWidth="21600" windowHeight="11820" tabRatio="722" firstSheet="16" activeTab="20" xr2:uid="{977D219B-3D5A-4B74-BC43-A61DD328A31A}"/>
   </bookViews>
   <sheets>
     <sheet name="1HTML_scratch" sheetId="9" r:id="rId1"/>
@@ -34,9 +34,9 @@
     <sheet name="19Vue_comp" sheetId="16" r:id="rId19"/>
     <sheet name="Vue3" sheetId="23" r:id="rId20"/>
     <sheet name="Vue3_new" sheetId="24" r:id="rId21"/>
-    <sheet name="Lowcode_proj" sheetId="25" r:id="rId22"/>
-    <sheet name="Miniapp" sheetId="17" r:id="rId23"/>
-    <sheet name="NodeJS" sheetId="26" r:id="rId24"/>
+    <sheet name="NodeJS" sheetId="26" r:id="rId22"/>
+    <sheet name="Lowcode_proj" sheetId="25" r:id="rId23"/>
+    <sheet name="Miniapp" sheetId="17" r:id="rId24"/>
     <sheet name="TS_complete" sheetId="27" r:id="rId25"/>
     <sheet name="TS_basic" sheetId="28" r:id="rId26"/>
     <sheet name="TS_pro" sheetId="29" r:id="rId27"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="1204">
   <si>
     <t>1. 环境准备</t>
   </si>
@@ -3695,6 +3695,46 @@
   </si>
   <si>
     <t>18 19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将实测代码放到根目录下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4 5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7 9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前台使用后端接口数据，修复前台Bug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修复分页列表Bug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7 9 10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重新设计页面、修复登录Bug、后端ico上传Bug</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 11 12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3705,7 +3745,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="hh:mm:ss"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3838,6 +3878,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -3953,7 +4001,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4218,10 +4266,19 @@
     <xf numFmtId="58" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="46" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="46" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5137,6 +5194,10 @@
       <c r="A2" s="32" t="s">
         <v>388</v>
       </c>
+      <c r="D2" s="91" t="str">
+        <f t="shared" ref="D2:D33" si="0">IF(ISBLANK(C2),"",B2/1440+C2/86400)</f>
+        <v/>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -5148,6 +5209,10 @@
       <c r="C3">
         <v>27</v>
       </c>
+      <c r="D3" s="91">
+        <f t="shared" si="0"/>
+        <v>2.8090277777777777E-2</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -5159,6 +5224,10 @@
       <c r="C4">
         <v>3</v>
       </c>
+      <c r="D4" s="91">
+        <f t="shared" si="0"/>
+        <v>5.6284722222222222E-2</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -5170,11 +5239,19 @@
       <c r="C5">
         <v>52</v>
       </c>
+      <c r="D5" s="91">
+        <f t="shared" si="0"/>
+        <v>1.0324074074074074E-2</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="32" t="s">
         <v>391</v>
       </c>
+      <c r="D6" s="91" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -5186,6 +5263,10 @@
       <c r="C7">
         <v>11</v>
       </c>
+      <c r="D7" s="91">
+        <f t="shared" si="0"/>
+        <v>2.7905092592592592E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -5197,6 +5278,10 @@
       <c r="C8">
         <v>45</v>
       </c>
+      <c r="D8" s="91">
+        <f t="shared" si="0"/>
+        <v>4.565972222222222E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -5208,6 +5293,10 @@
       <c r="C9">
         <v>9</v>
       </c>
+      <c r="D9" s="91">
+        <f t="shared" si="0"/>
+        <v>3.6215277777777777E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -5219,6 +5308,10 @@
       <c r="C10">
         <v>40</v>
       </c>
+      <c r="D10" s="91">
+        <f t="shared" si="0"/>
+        <v>5.949074074074074E-2</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -5230,11 +5323,19 @@
       <c r="C11">
         <v>23</v>
       </c>
+      <c r="D11" s="91">
+        <f t="shared" si="0"/>
+        <v>4.8182870370370376E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="32" t="s">
         <v>397</v>
       </c>
+      <c r="D12" s="91" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -5246,6 +5347,10 @@
       <c r="C13">
         <v>9</v>
       </c>
+      <c r="D13" s="91">
+        <f t="shared" si="0"/>
+        <v>2.5798611111111109E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -5257,6 +5362,10 @@
       <c r="C14">
         <v>1</v>
       </c>
+      <c r="D14" s="91">
+        <f t="shared" si="0"/>
+        <v>4.0289351851851854E-2</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -5268,6 +5377,10 @@
       <c r="C15">
         <v>17</v>
       </c>
+      <c r="D15" s="91">
+        <f t="shared" si="0"/>
+        <v>6.4467592592592597E-3</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -5279,8 +5392,12 @@
       <c r="C16">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16" s="91">
+        <f t="shared" si="0"/>
+        <v>3.1458333333333331E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>402</v>
       </c>
@@ -5290,8 +5407,12 @@
       <c r="C17">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17" s="91">
+        <f t="shared" si="0"/>
+        <v>3.1469907407407405E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>403</v>
       </c>
@@ -5301,8 +5422,12 @@
       <c r="C18">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18" s="91">
+        <f t="shared" si="0"/>
+        <v>3.7673611111111109E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>404</v>
       </c>
@@ -5312,8 +5437,12 @@
       <c r="C19">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19" s="91">
+        <f t="shared" si="0"/>
+        <v>6.7939814814814816E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>405</v>
       </c>
@@ -5323,8 +5452,12 @@
       <c r="C20">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20" s="91">
+        <f t="shared" si="0"/>
+        <v>5.3935185185185188E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>406</v>
       </c>
@@ -5334,8 +5467,12 @@
       <c r="C21">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21" s="91">
+        <f t="shared" si="0"/>
+        <v>2.162037037037037E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>407</v>
       </c>
@@ -5345,8 +5482,12 @@
       <c r="C22">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22" s="91">
+        <f t="shared" si="0"/>
+        <v>5.0902777777777776E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>408</v>
       </c>
@@ -5356,8 +5497,12 @@
       <c r="C23">
         <v>42</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23" s="91">
+        <f t="shared" si="0"/>
+        <v>3.6597222222222218E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>409</v>
       </c>
@@ -5367,13 +5512,21 @@
       <c r="C24">
         <v>37</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24" s="91">
+        <f t="shared" si="0"/>
+        <v>1.2928240740740742E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="32" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25" s="91" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>411</v>
       </c>
@@ -5383,8 +5536,12 @@
       <c r="C26">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D26" s="91">
+        <f t="shared" si="0"/>
+        <v>1.3391203703703704E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>412</v>
       </c>
@@ -5394,8 +5551,12 @@
       <c r="C27">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27" s="91">
+        <f t="shared" si="0"/>
+        <v>2.9189814814814814E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>413</v>
       </c>
@@ -5405,8 +5566,12 @@
       <c r="C28">
         <v>32</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D28" s="91">
+        <f t="shared" si="0"/>
+        <v>2.5370370370370373E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>414</v>
       </c>
@@ -5416,8 +5581,12 @@
       <c r="C29">
         <v>57</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D29" s="91">
+        <f t="shared" si="0"/>
+        <v>5.5208333333333333E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>415</v>
       </c>
@@ -5427,8 +5596,12 @@
       <c r="C30">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D30" s="91">
+        <f t="shared" si="0"/>
+        <v>3.5046296296296298E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>416</v>
       </c>
@@ -5438,8 +5611,12 @@
       <c r="C31">
         <v>51</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D31" s="91">
+        <f t="shared" si="0"/>
+        <v>3.0451388888888889E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>417</v>
       </c>
@@ -5449,8 +5626,12 @@
       <c r="C32">
         <v>45</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32" s="91">
+        <f t="shared" si="0"/>
+        <v>2.8298611111111111E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>418</v>
       </c>
@@ -5460,8 +5641,12 @@
       <c r="C33">
         <v>46</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D33" s="91">
+        <f t="shared" si="0"/>
+        <v>6.7199074074074078E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>419</v>
       </c>
@@ -5471,8 +5656,12 @@
       <c r="C34">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34" s="91">
+        <f t="shared" ref="D34:D65" si="1">IF(ISBLANK(C34),"",B34/1440+C34/86400)</f>
+        <v>1.6018518518518519E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>420</v>
       </c>
@@ -5482,13 +5671,21 @@
       <c r="C35">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35" s="91">
+        <f t="shared" si="1"/>
+        <v>4.7974537037037038E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="32" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>422</v>
       </c>
@@ -5498,8 +5695,12 @@
       <c r="C37">
         <v>48</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D37" s="91">
+        <f t="shared" si="1"/>
+        <v>5.1944444444444439E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>423</v>
       </c>
@@ -5509,8 +5710,12 @@
       <c r="C38">
         <v>8</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38" s="91">
+        <f t="shared" si="1"/>
+        <v>4.175925925925926E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>424</v>
       </c>
@@ -5520,8 +5725,12 @@
       <c r="C39">
         <v>56</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39" s="91">
+        <f t="shared" si="1"/>
+        <v>2.9120370370370369E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>425</v>
       </c>
@@ -5531,8 +5740,12 @@
       <c r="C40">
         <v>59</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D40" s="91">
+        <f t="shared" si="1"/>
+        <v>4.3043981481481482E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>426</v>
       </c>
@@ -5542,8 +5755,12 @@
       <c r="C41">
         <v>11</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D41" s="91">
+        <f t="shared" si="1"/>
+        <v>2.6516203703703705E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>427</v>
       </c>
@@ -5553,8 +5770,12 @@
       <c r="C42">
         <v>31</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D42" s="91">
+        <f t="shared" si="1"/>
+        <v>3.9942129629629626E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>428</v>
       </c>
@@ -5564,8 +5785,12 @@
       <c r="C43">
         <v>32</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D43" s="91">
+        <f t="shared" si="1"/>
+        <v>2.6064814814814815E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>429</v>
       </c>
@@ -5575,13 +5800,21 @@
       <c r="C44">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D44" s="91">
+        <f t="shared" si="1"/>
+        <v>4.3784722222222218E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="32" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D45" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>431</v>
       </c>
@@ -5591,8 +5824,12 @@
       <c r="C46">
         <v>59</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D46" s="91">
+        <f t="shared" si="1"/>
+        <v>4.7905092592592589E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>432</v>
       </c>
@@ -5602,8 +5839,12 @@
       <c r="C47">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D47" s="91">
+        <f t="shared" si="1"/>
+        <v>4.1863425925925922E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>433</v>
       </c>
@@ -5613,8 +5854,12 @@
       <c r="C48">
         <v>54</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D48" s="91">
+        <f t="shared" si="1"/>
+        <v>2.0138888888888888E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>434</v>
       </c>
@@ -5624,8 +5869,12 @@
       <c r="C49">
         <v>59</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D49" s="91">
+        <f t="shared" si="1"/>
+        <v>5.4155092592592588E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>435</v>
       </c>
@@ -5635,8 +5884,12 @@
       <c r="C50">
         <v>51</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D50" s="91">
+        <f t="shared" si="1"/>
+        <v>2.7673611111111111E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>436</v>
       </c>
@@ -5646,8 +5899,12 @@
       <c r="C51">
         <v>30</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D51" s="91">
+        <f t="shared" si="1"/>
+        <v>8.6805555555555559E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>437</v>
       </c>
@@ -5657,8 +5914,12 @@
       <c r="C52">
         <v>22</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D52" s="91">
+        <f t="shared" si="1"/>
+        <v>4.1226851851851855E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>438</v>
       </c>
@@ -5668,8 +5929,12 @@
       <c r="C53">
         <v>17</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D53" s="91">
+        <f t="shared" si="1"/>
+        <v>2.5891203703703701E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>439</v>
       </c>
@@ -5679,8 +5944,12 @@
       <c r="C54">
         <v>58</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D54" s="91">
+        <f t="shared" si="1"/>
+        <v>4.2337962962962959E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>440</v>
       </c>
@@ -5690,8 +5959,12 @@
       <c r="C55">
         <v>21</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D55" s="91">
+        <f t="shared" si="1"/>
+        <v>4.6076388888888889E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>441</v>
       </c>
@@ -5701,8 +5974,12 @@
       <c r="C56">
         <v>20</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D56" s="91">
+        <f t="shared" si="1"/>
+        <v>4.1898148148148143E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>442</v>
       </c>
@@ -5712,13 +5989,21 @@
       <c r="C57">
         <v>22</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D57" s="91">
+        <f t="shared" si="1"/>
+        <v>4.1226851851851855E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="32" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D58" s="91" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>444</v>
       </c>
@@ -5728,8 +6013,12 @@
       <c r="C59">
         <v>19</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D59" s="91">
+        <f t="shared" si="1"/>
+        <v>2.7303240740740743E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>445</v>
       </c>
@@ -5739,8 +6028,12 @@
       <c r="C60">
         <v>42</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D60" s="91">
+        <f t="shared" si="1"/>
+        <v>4.701388888888889E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>446</v>
       </c>
@@ -5750,8 +6043,12 @@
       <c r="C61">
         <v>46</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D61" s="91">
+        <f t="shared" si="1"/>
+        <v>1.1643518518518518E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>447</v>
       </c>
@@ -5761,8 +6058,12 @@
       <c r="C62">
         <v>57</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D62" s="91">
+        <f t="shared" si="1"/>
+        <v>3.815972222222222E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>448</v>
       </c>
@@ -5772,8 +6073,12 @@
       <c r="C63">
         <v>52</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D63" s="91">
+        <f t="shared" si="1"/>
+        <v>3.4629629629629628E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>449</v>
       </c>
@@ -5783,8 +6088,12 @@
       <c r="C64">
         <v>53</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D64" s="91">
+        <f t="shared" si="1"/>
+        <v>3.8807870370370375E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>450</v>
       </c>
@@ -5794,8 +6103,12 @@
       <c r="C65">
         <v>49</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D65" s="91">
+        <f t="shared" si="1"/>
+        <v>3.1817129629629633E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>451</v>
       </c>
@@ -5805,8 +6118,12 @@
       <c r="C66">
         <v>32</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D66" s="91">
+        <f t="shared" ref="D66:D97" si="2">IF(ISBLANK(C66),"",B66/1440+C66/86400)</f>
+        <v>1.4259259259259258E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>452</v>
       </c>
@@ -5816,8 +6133,12 @@
       <c r="C67">
         <v>55</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D67" s="91">
+        <f t="shared" si="2"/>
+        <v>4.0914351851851855E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>453</v>
       </c>
@@ -5827,13 +6148,21 @@
       <c r="C68">
         <v>31</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D68" s="91">
+        <f t="shared" si="2"/>
+        <v>2.3275462962962963E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="32" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D69" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>455</v>
       </c>
@@ -5843,8 +6172,12 @@
       <c r="C70">
         <v>22</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D70" s="91">
+        <f t="shared" si="2"/>
+        <v>1.5532407407407406E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>456</v>
       </c>
@@ -5854,8 +6187,12 @@
       <c r="C71">
         <v>10</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D71" s="91">
+        <f t="shared" si="2"/>
+        <v>2.5115740740740741E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>457</v>
       </c>
@@ -5865,8 +6202,12 @@
       <c r="C72">
         <v>15</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D72" s="91">
+        <f t="shared" si="2"/>
+        <v>3.6979166666666667E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>458</v>
       </c>
@@ -5876,8 +6217,12 @@
       <c r="C73">
         <v>13</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D73" s="91">
+        <f t="shared" si="2"/>
+        <v>2.4456018518518519E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>459</v>
       </c>
@@ -5887,8 +6232,12 @@
       <c r="C74">
         <v>30</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D74" s="91">
+        <f t="shared" si="2"/>
+        <v>4.2708333333333334E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>460</v>
       </c>
@@ -5898,8 +6247,12 @@
       <c r="C75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D75" s="91">
+        <f t="shared" si="2"/>
+        <v>5.486111111111111E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>461</v>
       </c>
@@ -5909,8 +6262,12 @@
       <c r="C76">
         <v>15</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D76" s="91">
+        <f t="shared" si="2"/>
+        <v>1.4062499999999999E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>462</v>
       </c>
@@ -5920,8 +6277,12 @@
       <c r="C77">
         <v>42</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D77" s="91">
+        <f t="shared" si="2"/>
+        <v>1.5069444444444444E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>463</v>
       </c>
@@ -5931,8 +6292,12 @@
       <c r="C78">
         <v>39</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D78" s="91">
+        <f t="shared" si="2"/>
+        <v>2.4756944444444446E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>464</v>
       </c>
@@ -5942,8 +6307,12 @@
       <c r="C79">
         <v>42</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D79" s="91">
+        <f t="shared" si="2"/>
+        <v>3.5902777777777777E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>465</v>
       </c>
@@ -5953,8 +6322,12 @@
       <c r="C80">
         <v>28</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D80" s="91">
+        <f t="shared" si="2"/>
+        <v>3.1574074074074074E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>466</v>
       </c>
@@ -5964,8 +6337,12 @@
       <c r="C81">
         <v>17</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D81" s="91">
+        <f t="shared" si="2"/>
+        <v>9.9189814814814817E-3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>467</v>
       </c>
@@ -5975,8 +6352,12 @@
       <c r="C82">
         <v>36</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D82" s="91">
+        <f t="shared" si="2"/>
+        <v>4.2083333333333334E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>468</v>
       </c>
@@ -5986,13 +6367,21 @@
       <c r="C83">
         <v>37</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D83" s="91">
+        <f t="shared" si="2"/>
+        <v>3.4456018518518518E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="32" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D84" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>470</v>
       </c>
@@ -6002,8 +6391,12 @@
       <c r="C85">
         <v>54</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D85" s="91">
+        <f t="shared" si="2"/>
+        <v>2.5625000000000002E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>471</v>
       </c>
@@ -6013,8 +6406,12 @@
       <c r="C86">
         <v>14</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D86" s="91">
+        <f t="shared" si="2"/>
+        <v>1.474537037037037E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>472</v>
       </c>
@@ -6024,8 +6421,12 @@
       <c r="C87">
         <v>56</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D87" s="91">
+        <f t="shared" si="2"/>
+        <v>7.3564814814814819E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>473</v>
       </c>
@@ -6035,8 +6436,12 @@
       <c r="C88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D88" s="91">
+        <f t="shared" si="2"/>
+        <v>2.8472222222222222E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>474</v>
       </c>
@@ -6046,13 +6451,21 @@
       <c r="C89">
         <v>21</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D89" s="91">
+        <f t="shared" si="2"/>
+        <v>4.3298611111111114E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="32" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D90" s="91" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>476</v>
       </c>
@@ -6062,8 +6475,12 @@
       <c r="C91">
         <v>49</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D91" s="91">
+        <f t="shared" si="2"/>
+        <v>4.8483796296296303E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>477</v>
       </c>
@@ -6073,8 +6490,12 @@
       <c r="C92">
         <v>44</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D92" s="91">
+        <f t="shared" si="2"/>
+        <v>4.8425925925925928E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>478</v>
       </c>
@@ -6084,8 +6505,12 @@
       <c r="C93">
         <v>57</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D93" s="91">
+        <f t="shared" si="2"/>
+        <v>4.3715277777777777E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>479</v>
       </c>
@@ -6095,8 +6520,12 @@
       <c r="C94">
         <v>53</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D94" s="91">
+        <f t="shared" si="2"/>
+        <v>5.3391203703703705E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>480</v>
       </c>
@@ -6106,8 +6535,12 @@
       <c r="C95">
         <v>25</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D95" s="91">
+        <f t="shared" si="2"/>
+        <v>4.4733796296296299E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>481</v>
       </c>
@@ -6117,8 +6550,12 @@
       <c r="C96">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D96" s="91">
+        <f t="shared" si="2"/>
+        <v>2.9201388888888888E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>482</v>
       </c>
@@ -6128,8 +6565,12 @@
       <c r="C97">
         <v>13</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D97" s="91">
+        <f t="shared" si="2"/>
+        <v>3.0706018518518518E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>483</v>
       </c>
@@ -6139,8 +6580,12 @@
       <c r="C98">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D98" s="91">
+        <f t="shared" ref="D98:D113" si="3">IF(ISBLANK(C98),"",B98/1440+C98/86400)</f>
+        <v>2.7083333333333334E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>484</v>
       </c>
@@ -6150,8 +6595,12 @@
       <c r="C99">
         <v>7</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D99" s="91">
+        <f t="shared" si="3"/>
+        <v>2.1608796296296296E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>485</v>
       </c>
@@ -6161,13 +6610,21 @@
       <c r="C100">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D100" s="91">
+        <f t="shared" si="3"/>
+        <v>1.4618055555555556E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="32" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D101" s="91" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>487</v>
       </c>
@@ -6177,8 +6634,12 @@
       <c r="C102">
         <v>56</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D102" s="91">
+        <f t="shared" si="3"/>
+        <v>4.7175925925925927E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>488</v>
       </c>
@@ -6188,8 +6649,12 @@
       <c r="C103">
         <v>35</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D103" s="91">
+        <f t="shared" si="3"/>
+        <v>3.5821759259259262E-2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>489</v>
       </c>
@@ -6199,8 +6664,12 @@
       <c r="C104">
         <v>48</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D104" s="91">
+        <f t="shared" si="3"/>
+        <v>2.0694444444444446E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>490</v>
       </c>
@@ -6210,8 +6679,12 @@
       <c r="C105">
         <v>6</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D105" s="91">
+        <f t="shared" si="3"/>
+        <v>2.0902777777777777E-2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>491</v>
       </c>
@@ -6221,8 +6694,12 @@
       <c r="C106">
         <v>4</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D106" s="91">
+        <f t="shared" si="3"/>
+        <v>3.0601851851851852E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>492</v>
       </c>
@@ -6232,8 +6709,12 @@
       <c r="C107">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D107" s="91">
+        <f t="shared" si="3"/>
+        <v>4.1689814814814811E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>493</v>
       </c>
@@ -6243,8 +6724,12 @@
       <c r="C108">
         <v>43</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D108" s="91">
+        <f t="shared" si="3"/>
+        <v>3.8692129629629632E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>494</v>
       </c>
@@ -6254,8 +6739,12 @@
       <c r="C109">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D109" s="91">
+        <f t="shared" si="3"/>
+        <v>4.3773148148148144E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>495</v>
       </c>
@@ -6265,8 +6754,12 @@
       <c r="C110">
         <v>48</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D110" s="91">
+        <f t="shared" si="3"/>
+        <v>4.2222222222222217E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>496</v>
       </c>
@@ -6276,13 +6769,21 @@
       <c r="C111">
         <v>22</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D111" s="91">
+        <f t="shared" si="3"/>
+        <v>6.06712962962963E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="32" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D112" s="91" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>498</v>
       </c>
@@ -6292,8 +6793,12 @@
       <c r="C113">
         <v>19</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D113" s="91">
+        <f t="shared" si="3"/>
+        <v>7.858796296296296E-3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" s="34" t="str">
         <f>"总时长："&amp;TEXT(SUM(B:B)/1440+SUM(C:C)/86400,"[h]:mm:ss")</f>
         <v>总时长：79:03:38</v>
@@ -9120,6 +9625,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.2">
@@ -9152,7 +9658,7 @@
       <c r="C2" s="57">
         <v>15</v>
       </c>
-      <c r="D2" s="89">
+      <c r="D2" s="88">
         <f>B2/1440+C2/86400</f>
         <v>1.3368055555555555E-2</v>
       </c>
@@ -9170,7 +9676,7 @@
       <c r="C3" s="57">
         <v>29</v>
       </c>
-      <c r="D3" s="89">
+      <c r="D3" s="88">
         <f>B3/1440+C3/86400</f>
         <v>1.6307870370370368E-2</v>
       </c>
@@ -9188,7 +9694,7 @@
       <c r="C4" s="57">
         <v>31</v>
       </c>
-      <c r="D4" s="89">
+      <c r="D4" s="88">
         <f>B4/1440+C4/86400</f>
         <v>1.7025462962962964E-2</v>
       </c>
@@ -9197,501 +9703,519 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="A5" s="57" t="s">
         <v>547</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="57">
         <v>32</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="57">
         <v>38</v>
       </c>
       <c r="D5" s="88">
         <f>B5/1440+C5/86400</f>
         <v>2.266203703703704E-2</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="45">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="A6" s="57" t="s">
         <v>548</v>
       </c>
-      <c r="E6" s="25"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="89" t="s">
         <v>565</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="57">
         <v>15</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="57">
         <v>39</v>
       </c>
       <c r="D7" s="88">
         <f t="shared" ref="D7:D21" si="0">B7/1440+C7/86400</f>
         <v>1.0868055555555554E-2</v>
       </c>
-      <c r="E7" s="25">
-        <v>2</v>
+      <c r="E7" s="45">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="89" t="s">
         <v>566</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="57">
         <v>58</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="57">
         <v>53</v>
       </c>
       <c r="D8" s="88">
         <f t="shared" si="0"/>
         <v>4.0891203703703707E-2</v>
       </c>
-      <c r="E8" s="25">
-        <v>2</v>
+      <c r="E8" s="45">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="89" t="s">
         <v>567</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="57">
         <v>17</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="57">
         <v>33</v>
       </c>
       <c r="D9" s="88">
         <f t="shared" si="0"/>
         <v>1.21875E-2</v>
       </c>
-      <c r="E9" s="25">
-        <v>2</v>
+      <c r="E9" s="45">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="A10" s="57" t="s">
         <v>549</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="57">
         <v>62</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="57">
         <v>48</v>
       </c>
       <c r="D10" s="88">
         <f t="shared" si="0"/>
         <v>4.3611111111111107E-2</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="45">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="A11" s="57" t="s">
         <v>550</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="57">
         <v>46</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="57">
         <v>58</v>
       </c>
       <c r="D11" s="88">
         <f t="shared" si="0"/>
         <v>3.2615740740740737E-2</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="45">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="A12" s="57" t="s">
         <v>551</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="57">
         <v>58</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="57">
         <v>58</v>
       </c>
       <c r="D12" s="88">
         <f t="shared" si="0"/>
         <v>4.0949074074074075E-2</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="45">
         <v>4</v>
       </c>
+      <c r="F12" s="90">
+        <v>46078</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="A13" s="57" t="s">
         <v>552</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="57">
         <v>40</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="57">
         <v>28</v>
       </c>
       <c r="D13" s="88">
         <f t="shared" si="0"/>
         <v>2.810185185185185E-2</v>
       </c>
-      <c r="E13" s="25">
-        <v>5</v>
+      <c r="E13" s="45">
+        <v>4</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1194</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="A14" s="57" t="s">
         <v>553</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="57">
         <v>57</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="57">
         <v>4</v>
       </c>
       <c r="D14" s="88">
         <f t="shared" si="0"/>
         <v>3.9629629629629626E-2</v>
       </c>
-      <c r="E14" s="25">
-        <v>5</v>
+      <c r="E14" s="45" t="s">
+        <v>1195</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="A15" s="57" t="s">
         <v>554</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="57">
         <v>78</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="57">
         <v>32</v>
       </c>
       <c r="D15" s="88">
         <f t="shared" si="0"/>
         <v>5.4537037037037037E-2</v>
       </c>
-      <c r="E15" s="25">
-        <v>6</v>
+      <c r="E15" s="45" t="s">
+        <v>1196</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="A16" s="57" t="s">
         <v>555</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="57">
         <v>43</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="57">
         <v>35</v>
       </c>
       <c r="D16" s="88">
         <f t="shared" si="0"/>
         <v>3.0266203703703705E-2</v>
       </c>
-      <c r="E16" s="25">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="E16" s="45" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="57" t="s">
         <v>556</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="57">
         <v>79</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="57">
         <v>53</v>
       </c>
       <c r="D17" s="88">
         <f t="shared" si="0"/>
         <v>5.5474537037037037E-2</v>
       </c>
-      <c r="E17" s="25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="E17" s="45" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="57" t="s">
         <v>557</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="57">
         <v>15</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="57">
         <v>47</v>
       </c>
       <c r="D18" s="88">
         <f t="shared" si="0"/>
         <v>1.0960648148148148E-2</v>
       </c>
-      <c r="E18" s="25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="E18" s="45" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="57" t="s">
         <v>558</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="57">
         <v>75</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="57">
         <v>6</v>
       </c>
       <c r="D19" s="88">
         <f t="shared" si="0"/>
         <v>5.2152777777777777E-2</v>
       </c>
-      <c r="E19" s="25">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="E19" s="45" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="57" t="s">
         <v>559</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="57">
         <v>14</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="57">
         <v>46</v>
       </c>
       <c r="D20" s="88">
         <f t="shared" si="0"/>
         <v>1.0254629629629629E-2</v>
       </c>
-      <c r="E20" s="25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="E20" s="45" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="57" t="s">
         <v>560</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="57">
         <v>35</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="57">
         <v>52</v>
       </c>
       <c r="D21" s="88">
         <f t="shared" si="0"/>
         <v>2.4907407407407409E-2</v>
       </c>
-      <c r="E21" s="25">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E21" s="45" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>561</v>
       </c>
       <c r="E22" s="25"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="57" t="s">
         <v>568</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="57">
         <v>8</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="57">
         <v>28</v>
       </c>
       <c r="D23" s="88">
         <f t="shared" ref="D23:D33" si="1">B23/1440+C23/86400</f>
         <v>5.8796296296296296E-3</v>
       </c>
-      <c r="E23" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="E23" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="57" t="s">
         <v>569</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="57">
         <v>17</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="57">
         <v>10</v>
       </c>
       <c r="D24" s="88">
         <f t="shared" si="1"/>
         <v>1.1921296296296296E-2</v>
       </c>
-      <c r="E24" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="E24" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="57" t="s">
         <v>570</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="57">
         <v>5</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="57">
         <v>25</v>
       </c>
       <c r="D25" s="88">
         <f t="shared" si="1"/>
         <v>3.7615740740740739E-3</v>
       </c>
-      <c r="E25" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="E25" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="57" t="s">
         <v>571</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="57">
         <v>13</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="57">
         <v>16</v>
       </c>
       <c r="D26" s="88">
         <f t="shared" si="1"/>
         <v>9.2129629629629627E-3</v>
       </c>
-      <c r="E26" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="E26" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="57" t="s">
         <v>572</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="57">
         <v>23</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="57">
         <v>23</v>
       </c>
       <c r="D27" s="88">
         <f t="shared" si="1"/>
         <v>1.6238425925925924E-2</v>
       </c>
-      <c r="E27" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="E27" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="57" t="s">
         <v>573</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="57">
         <v>8</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="57">
         <v>57</v>
       </c>
       <c r="D28" s="88">
         <f t="shared" si="1"/>
         <v>6.2152777777777779E-3</v>
       </c>
-      <c r="E28" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="E28" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="57" t="s">
         <v>574</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="57">
         <v>18</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="57">
         <v>46</v>
       </c>
       <c r="D29" s="88">
         <f t="shared" si="1"/>
         <v>1.3032407407407407E-2</v>
       </c>
-      <c r="E29" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="E29" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="57" t="s">
         <v>575</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="57">
         <v>5</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="57">
         <v>55</v>
       </c>
       <c r="D30" s="88">
         <f t="shared" si="1"/>
         <v>4.1087962962962962E-3</v>
       </c>
-      <c r="E30" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="E30" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="57" t="s">
         <v>576</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="57">
         <v>4</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="57">
         <v>21</v>
       </c>
       <c r="D31" s="88">
         <f t="shared" si="1"/>
         <v>3.0208333333333333E-3</v>
       </c>
-      <c r="E31" s="25">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="E31" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="57" t="s">
         <v>577</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="57">
         <v>22</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="57">
         <v>55</v>
       </c>
       <c r="D32" s="88">
         <f t="shared" si="1"/>
         <v>1.5914351851851853E-2</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="45" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="57" t="s">
+        <v>562</v>
+      </c>
+      <c r="B33" s="57">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>562</v>
-      </c>
-      <c r="B33">
-        <v>10</v>
-      </c>
-      <c r="C33">
+      <c r="C33" s="57">
         <v>39</v>
       </c>
       <c r="D33" s="88">
         <f t="shared" si="1"/>
         <v>7.3958333333333333E-3</v>
       </c>
-      <c r="E33" s="25">
-        <v>10</v>
+      <c r="E33" s="45" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -9701,39 +10225,39 @@
       <c r="E34" s="25"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="A35" s="57" t="s">
         <v>578</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="57">
         <v>23</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="57">
         <v>38</v>
       </c>
       <c r="D35" s="88">
         <f>B35/1440+C35/86400</f>
         <v>1.6412037037037037E-2</v>
       </c>
-      <c r="E35" s="25">
-        <v>11</v>
+      <c r="E35" s="45" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+      <c r="A36" s="57" t="s">
         <v>579</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="57">
         <v>26</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="57">
         <v>6</v>
       </c>
       <c r="D36" s="88">
         <f>B36/1440+C36/86400</f>
         <v>1.8124999999999999E-2</v>
       </c>
-      <c r="E36" s="25">
-        <v>11</v>
+      <c r="E36" s="45" t="s">
+        <v>1203</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -9759,6 +10283,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -11021,6 +11546,10 @@
       <c r="C3">
         <v>10</v>
       </c>
+      <c r="D3" s="91">
+        <f t="shared" ref="D3:D34" si="0">B3/1440+C3/86400</f>
+        <v>9.1435185185185178E-3</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -11032,11 +11561,20 @@
       <c r="C4">
         <v>24</v>
       </c>
+      <c r="D4" s="91">
+        <f t="shared" si="0"/>
+        <v>1.0694444444444444E-2</v>
+      </c>
+      <c r="E4" s="92">
+        <f>SUM(D3:D4)</f>
+        <v>1.983796296296296E-2</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>767</v>
       </c>
+      <c r="D5" s="91"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -11048,6 +11586,10 @@
       <c r="C6">
         <v>27</v>
       </c>
+      <c r="D6" s="91">
+        <f t="shared" si="0"/>
+        <v>1.4895833333333334E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
@@ -11059,6 +11601,10 @@
       <c r="C7">
         <v>25</v>
       </c>
+      <c r="D7" s="91">
+        <f t="shared" si="0"/>
+        <v>2.3206018518518518E-2</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="36" t="s">
@@ -11070,6 +11616,10 @@
       <c r="C8">
         <v>25</v>
       </c>
+      <c r="D8" s="91">
+        <f t="shared" si="0"/>
+        <v>2.8067129629629629E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="36" t="s">
@@ -11081,6 +11631,10 @@
       <c r="C9">
         <v>39</v>
       </c>
+      <c r="D9" s="91">
+        <f t="shared" si="0"/>
+        <v>2.1979166666666668E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -11092,6 +11646,10 @@
       <c r="C10">
         <v>19</v>
       </c>
+      <c r="D10" s="91">
+        <f t="shared" si="0"/>
+        <v>3.4942129629629629E-2</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -11103,6 +11661,10 @@
       <c r="C11">
         <v>43</v>
       </c>
+      <c r="D11" s="91">
+        <f t="shared" si="0"/>
+        <v>2.1331018518518517E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -11114,6 +11676,10 @@
       <c r="C12">
         <v>1</v>
       </c>
+      <c r="D12" s="91">
+        <f t="shared" si="0"/>
+        <v>3.2650462962962964E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -11125,6 +11691,10 @@
       <c r="C13">
         <v>9</v>
       </c>
+      <c r="D13" s="91">
+        <f t="shared" si="0"/>
+        <v>2.3715277777777776E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -11136,6 +11706,10 @@
       <c r="C14">
         <v>49</v>
       </c>
+      <c r="D14" s="91">
+        <f t="shared" si="0"/>
+        <v>3.2511574074074075E-2</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -11147,6 +11721,10 @@
       <c r="C15">
         <v>11</v>
       </c>
+      <c r="D15" s="91">
+        <f t="shared" si="0"/>
+        <v>2.8599537037037038E-2</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -11158,8 +11736,12 @@
       <c r="C16">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D16" s="91">
+        <f t="shared" si="0"/>
+        <v>3.4768518518518518E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>779</v>
       </c>
@@ -11169,8 +11751,12 @@
       <c r="C17">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17" s="91">
+        <f t="shared" si="0"/>
+        <v>2.3842592592592592E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>780</v>
       </c>
@@ -11180,8 +11766,12 @@
       <c r="C18">
         <v>57</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D18" s="91">
+        <f t="shared" si="0"/>
+        <v>2.2881944444444444E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>781</v>
       </c>
@@ -11191,8 +11781,12 @@
       <c r="C19">
         <v>37</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D19" s="91">
+        <f t="shared" si="0"/>
+        <v>3.7928240740740742E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>782</v>
       </c>
@@ -11202,8 +11796,12 @@
       <c r="C20">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D20" s="91">
+        <f t="shared" si="0"/>
+        <v>2.315972222222222E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>783</v>
       </c>
@@ -11213,8 +11811,12 @@
       <c r="C21">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D21" s="91">
+        <f t="shared" si="0"/>
+        <v>2.1111111111111108E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>784</v>
       </c>
@@ -11224,8 +11826,12 @@
       <c r="C22">
         <v>48</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D22" s="91">
+        <f t="shared" si="0"/>
+        <v>2.2083333333333333E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>785</v>
       </c>
@@ -11235,8 +11841,12 @@
       <c r="C23">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D23" s="91">
+        <f t="shared" si="0"/>
+        <v>2.7812499999999997E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>786</v>
       </c>
@@ -11246,8 +11856,12 @@
       <c r="C24">
         <v>26</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D24" s="91">
+        <f t="shared" si="0"/>
+        <v>3.0162037037037039E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>787</v>
       </c>
@@ -11257,8 +11871,12 @@
       <c r="C25">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D25" s="91">
+        <f t="shared" si="0"/>
+        <v>2.3032407407407404E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>788</v>
       </c>
@@ -11268,8 +11886,12 @@
       <c r="C26">
         <v>37</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D26" s="91">
+        <f t="shared" si="0"/>
+        <v>2.3344907407407404E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>789</v>
       </c>
@@ -11279,8 +11901,12 @@
       <c r="C27">
         <v>44</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D27" s="91">
+        <f t="shared" si="0"/>
+        <v>2.9675925925925925E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>790</v>
       </c>
@@ -11290,8 +11916,12 @@
       <c r="C28">
         <v>28</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D28" s="91">
+        <f t="shared" si="0"/>
+        <v>1.699074074074074E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>791</v>
       </c>
@@ -11301,8 +11931,12 @@
       <c r="C29">
         <v>42</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D29" s="91">
+        <f t="shared" si="0"/>
+        <v>2.4791666666666667E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>792</v>
       </c>
@@ -11312,8 +11946,12 @@
       <c r="C30">
         <v>52</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D30" s="91">
+        <f t="shared" si="0"/>
+        <v>3.0462962962962966E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>793</v>
       </c>
@@ -11323,8 +11961,12 @@
       <c r="C31">
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D31" s="91">
+        <f t="shared" si="0"/>
+        <v>3.3402777777777774E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>794</v>
       </c>
@@ -11334,8 +11976,12 @@
       <c r="C32">
         <v>9</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D32" s="91">
+        <f t="shared" si="0"/>
+        <v>2.0937499999999998E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>795</v>
       </c>
@@ -11345,8 +11991,12 @@
       <c r="C33">
         <v>27</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D33" s="91">
+        <f t="shared" si="0"/>
+        <v>1.8368055555555554E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>796</v>
       </c>
@@ -11356,8 +12006,12 @@
       <c r="C34">
         <v>54</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D34" s="91">
+        <f t="shared" si="0"/>
+        <v>2.7708333333333335E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>797</v>
       </c>
@@ -11367,13 +12021,22 @@
       <c r="C35">
         <v>43</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D35" s="91">
+        <f t="shared" ref="D35:D66" si="1">B35/1440+C35/86400</f>
+        <v>4.355324074074074E-2</v>
+      </c>
+      <c r="E35" s="92">
+        <f>SUM(D6:D35)</f>
+        <v>0.7979166666666665</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D36" s="91"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>799</v>
       </c>
@@ -11383,8 +12046,12 @@
       <c r="C37">
         <v>22</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D37" s="91">
+        <f t="shared" si="1"/>
+        <v>1.275462962962963E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>800</v>
       </c>
@@ -11394,8 +12061,12 @@
       <c r="C38">
         <v>40</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D38" s="91">
+        <f t="shared" si="1"/>
+        <v>6.0879629629629631E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>801</v>
       </c>
@@ -11405,8 +12076,12 @@
       <c r="C39">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D39" s="91">
+        <f t="shared" si="1"/>
+        <v>4.1018518518518517E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>802</v>
       </c>
@@ -11416,8 +12091,12 @@
       <c r="C40">
         <v>5</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D40" s="91">
+        <f t="shared" si="1"/>
+        <v>1.6724537037037038E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>803</v>
       </c>
@@ -11427,8 +12106,12 @@
       <c r="C41">
         <v>53</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D41" s="91">
+        <f t="shared" si="1"/>
+        <v>4.1585648148148149E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>804</v>
       </c>
@@ -11438,8 +12121,12 @@
       <c r="C42">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D42" s="91">
+        <f t="shared" si="1"/>
+        <v>3.6249999999999998E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>805</v>
       </c>
@@ -11449,8 +12136,12 @@
       <c r="C43">
         <v>11</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D43" s="91">
+        <f t="shared" si="1"/>
+        <v>3.6932870370370373E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>806</v>
       </c>
@@ -11460,8 +12151,12 @@
       <c r="C44">
         <v>55</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D44" s="91">
+        <f t="shared" si="1"/>
+        <v>2.841435185185185E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>807</v>
       </c>
@@ -11471,8 +12166,12 @@
       <c r="C45">
         <v>6</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D45" s="91">
+        <f t="shared" si="1"/>
+        <v>3.8263888888888889E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>808</v>
       </c>
@@ -11482,8 +12181,12 @@
       <c r="C46">
         <v>32</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D46" s="91">
+        <f t="shared" si="1"/>
+        <v>3.0925925925925926E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>809</v>
       </c>
@@ -11493,8 +12196,12 @@
       <c r="C47">
         <v>42</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D47" s="91">
+        <f t="shared" si="1"/>
+        <v>3.5208333333333335E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>810</v>
       </c>
@@ -11504,8 +12211,12 @@
       <c r="C48">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D48" s="91">
+        <f t="shared" si="1"/>
+        <v>3.4050925925925922E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>811</v>
       </c>
@@ -11515,8 +12226,12 @@
       <c r="C49">
         <v>38</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D49" s="91">
+        <f t="shared" si="1"/>
+        <v>1.849537037037037E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>812</v>
       </c>
@@ -11526,8 +12241,12 @@
       <c r="C50">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D50" s="91">
+        <f t="shared" si="1"/>
+        <v>1.7372685185185185E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>813</v>
       </c>
@@ -11537,8 +12256,12 @@
       <c r="C51">
         <v>13</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D51" s="91">
+        <f t="shared" si="1"/>
+        <v>1.2650462962962964E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>814</v>
       </c>
@@ -11548,8 +12271,12 @@
       <c r="C52">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D52" s="91">
+        <f t="shared" si="1"/>
+        <v>2.2280092592592594E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>815</v>
       </c>
@@ -11559,8 +12286,12 @@
       <c r="C53">
         <v>58</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D53" s="91">
+        <f t="shared" si="1"/>
+        <v>2.5671296296296296E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>816</v>
       </c>
@@ -11570,8 +12301,12 @@
       <c r="C54">
         <v>44</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D54" s="91">
+        <f t="shared" si="1"/>
+        <v>4.3564814814814813E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>817</v>
       </c>
@@ -11581,8 +12316,12 @@
       <c r="C55">
         <v>17</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D55" s="91">
+        <f t="shared" si="1"/>
+        <v>2.6585648148148146E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>818</v>
       </c>
@@ -11592,8 +12331,12 @@
       <c r="C56">
         <v>47</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D56" s="91">
+        <f t="shared" si="1"/>
+        <v>1.7905092592592594E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>819</v>
       </c>
@@ -11603,8 +12346,12 @@
       <c r="C57">
         <v>17</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D57" s="91">
+        <f t="shared" si="1"/>
+        <v>2.3113425925925923E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>820</v>
       </c>
@@ -11614,13 +12361,22 @@
       <c r="C58">
         <v>36</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D58" s="91">
+        <f t="shared" si="1"/>
+        <v>3.097222222222222E-2</v>
+      </c>
+      <c r="E58" s="92">
+        <f>SUM(D37:D58)</f>
+        <v>0.65162037037037013</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="25" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D59" s="91"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>799</v>
       </c>
@@ -11630,8 +12386,12 @@
       <c r="C60">
         <v>9</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D60" s="91">
+        <f t="shared" si="1"/>
+        <v>4.2708333333333331E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>822</v>
       </c>
@@ -11641,8 +12401,12 @@
       <c r="C61">
         <v>36</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D61" s="91">
+        <f t="shared" si="1"/>
+        <v>1.2916666666666667E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>823</v>
       </c>
@@ -11652,8 +12416,12 @@
       <c r="C62">
         <v>54</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D62" s="91">
+        <f t="shared" si="1"/>
+        <v>2.2152777777777778E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>824</v>
       </c>
@@ -11663,8 +12431,12 @@
       <c r="C63">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D63" s="91">
+        <f t="shared" si="1"/>
+        <v>2.7106481481481481E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>825</v>
       </c>
@@ -11674,8 +12446,12 @@
       <c r="C64">
         <v>51</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D64" s="91">
+        <f t="shared" si="1"/>
+        <v>2.6979166666666665E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>826</v>
       </c>
@@ -11685,8 +12461,12 @@
       <c r="C65">
         <v>8</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D65" s="91">
+        <f t="shared" si="1"/>
+        <v>2.6481481481481481E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>827</v>
       </c>
@@ -11696,8 +12476,12 @@
       <c r="C66">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D66" s="91">
+        <f t="shared" si="1"/>
+        <v>4.5856481481481477E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>828</v>
       </c>
@@ -11707,8 +12491,12 @@
       <c r="C67">
         <v>59</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D67" s="91">
+        <f t="shared" ref="D67:D98" si="2">B67/1440+C67/86400</f>
+        <v>1.7349537037037038E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>829</v>
       </c>
@@ -11718,8 +12506,12 @@
       <c r="C68">
         <v>44</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D68" s="91">
+        <f t="shared" si="2"/>
+        <v>1.1620370370370371E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>830</v>
       </c>
@@ -11729,8 +12521,12 @@
       <c r="C69">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D69" s="91">
+        <f t="shared" si="2"/>
+        <v>1.1817129629629629E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>831</v>
       </c>
@@ -11740,8 +12536,12 @@
       <c r="C70">
         <v>36</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D70" s="91">
+        <f t="shared" si="2"/>
+        <v>1.7083333333333332E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>832</v>
       </c>
@@ -11751,8 +12551,12 @@
       <c r="C71">
         <v>34</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D71" s="91">
+        <f t="shared" si="2"/>
+        <v>2.1921296296296296E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>833</v>
       </c>
@@ -11762,8 +12566,12 @@
       <c r="C72">
         <v>59</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D72" s="91">
+        <f t="shared" si="2"/>
+        <v>1.5266203703703704E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>834</v>
       </c>
@@ -11773,8 +12581,12 @@
       <c r="C73">
         <v>49</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D73" s="91">
+        <f t="shared" si="2"/>
+        <v>1.5150462962962963E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>835</v>
       </c>
@@ -11784,8 +12596,12 @@
       <c r="C74">
         <v>28</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D74" s="91">
+        <f t="shared" si="2"/>
+        <v>1.4212962962962962E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>836</v>
       </c>
@@ -11795,8 +12611,12 @@
       <c r="C75">
         <v>20</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D75" s="91">
+        <f t="shared" si="2"/>
+        <v>2.0370370370370372E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>837</v>
       </c>
@@ -11806,8 +12626,12 @@
       <c r="C76">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D76" s="91">
+        <f t="shared" si="2"/>
+        <v>4.2546296296296297E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>838</v>
       </c>
@@ -11817,8 +12641,12 @@
       <c r="C77">
         <v>17</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D77" s="91">
+        <f t="shared" si="2"/>
+        <v>1.4780092592592593E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>839</v>
       </c>
@@ -11828,8 +12656,12 @@
       <c r="C78">
         <v>35</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D78" s="91">
+        <f t="shared" si="2"/>
+        <v>1.3599537037037037E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>840</v>
       </c>
@@ -11839,8 +12671,12 @@
       <c r="C79">
         <v>42</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D79" s="91">
+        <f t="shared" si="2"/>
+        <v>4.7708333333333332E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>841</v>
       </c>
@@ -11850,8 +12686,12 @@
       <c r="C80">
         <v>36</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D80" s="91">
+        <f t="shared" si="2"/>
+        <v>3.4444444444444444E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>842</v>
       </c>
@@ -11861,8 +12701,12 @@
       <c r="C81">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D81" s="91">
+        <f t="shared" si="2"/>
+        <v>2.027777777777778E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>843</v>
       </c>
@@ -11872,8 +12716,12 @@
       <c r="C82">
         <v>24</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D82" s="91">
+        <f t="shared" si="2"/>
+        <v>3.9861111111111111E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>844</v>
       </c>
@@ -11883,8 +12731,12 @@
       <c r="C83">
         <v>33</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D83" s="91">
+        <f t="shared" si="2"/>
+        <v>1.4270833333333333E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>845</v>
       </c>
@@ -11894,8 +12746,12 @@
       <c r="C84">
         <v>23</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D84" s="91">
+        <f t="shared" si="2"/>
+        <v>3.9849537037037037E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>846</v>
       </c>
@@ -11905,8 +12761,12 @@
       <c r="C85">
         <v>53</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D85" s="91">
+        <f t="shared" si="2"/>
+        <v>4.1585648148148149E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>847</v>
       </c>
@@ -11916,8 +12776,12 @@
       <c r="C86">
         <v>52</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D86" s="91">
+        <f t="shared" si="2"/>
+        <v>3.740740740740741E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>848</v>
       </c>
@@ -11927,8 +12791,12 @@
       <c r="C87">
         <v>7</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D87" s="91">
+        <f t="shared" si="2"/>
+        <v>2.0914351851851851E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>849</v>
       </c>
@@ -11938,8 +12806,12 @@
       <c r="C88">
         <v>21</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D88" s="91">
+        <f t="shared" si="2"/>
+        <v>1.1354166666666667E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>850</v>
       </c>
@@ -11949,8 +12821,12 @@
       <c r="C89">
         <v>32</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D89" s="91">
+        <f t="shared" si="2"/>
+        <v>1.1481481481481481E-2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>851</v>
       </c>
@@ -11960,8 +12836,12 @@
       <c r="C90">
         <v>51</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D90" s="91">
+        <f t="shared" si="2"/>
+        <v>3.8090277777777778E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>852</v>
       </c>
@@ -11971,8 +12851,12 @@
       <c r="C91">
         <v>54</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D91" s="91">
+        <f t="shared" si="2"/>
+        <v>1.6597222222222222E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>853</v>
       </c>
@@ -11982,8 +12866,12 @@
       <c r="C92">
         <v>6</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D92" s="91">
+        <f t="shared" si="2"/>
+        <v>3.0624999999999999E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>854</v>
       </c>
@@ -11993,8 +12881,12 @@
       <c r="C93">
         <v>30</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D93" s="91">
+        <f t="shared" si="2"/>
+        <v>1.8402777777777775E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>855</v>
       </c>
@@ -12004,8 +12896,12 @@
       <c r="C94">
         <v>17</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D94" s="91">
+        <f t="shared" si="2"/>
+        <v>4.4641203703703704E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>856</v>
       </c>
@@ -12015,8 +12911,12 @@
       <c r="C95">
         <v>22</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D95" s="91">
+        <f t="shared" si="2"/>
+        <v>1.8310185185185183E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>857</v>
       </c>
@@ -12026,8 +12926,12 @@
       <c r="C96">
         <v>10</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D96" s="91">
+        <f t="shared" si="2"/>
+        <v>3.0671296296296294E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>858</v>
       </c>
@@ -12037,8 +12941,12 @@
       <c r="C97">
         <v>43</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D97" s="91">
+        <f t="shared" si="2"/>
+        <v>2.1331018518518517E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>859</v>
       </c>
@@ -12048,8 +12956,12 @@
       <c r="C98">
         <v>16</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D98" s="91">
+        <f t="shared" si="2"/>
+        <v>3.2129629629629626E-2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>860</v>
       </c>
@@ -12059,8 +12971,12 @@
       <c r="C99">
         <v>24</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D99" s="91">
+        <f t="shared" ref="D99:D102" si="3">B99/1440+C99/86400</f>
+        <v>1.5555555555555555E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>861</v>
       </c>
@@ -12070,8 +12986,12 @@
       <c r="C100">
         <v>42</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D100" s="91">
+        <f t="shared" si="3"/>
+        <v>2.4097222222222221E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>862</v>
       </c>
@@ -12081,8 +13001,12 @@
       <c r="C101">
         <v>30</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D101" s="91">
+        <f t="shared" si="3"/>
+        <v>1.2847222222222223E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>863</v>
       </c>
@@ -12092,8 +13016,16 @@
       <c r="C102">
         <v>54</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D102" s="91">
+        <f t="shared" si="3"/>
+        <v>3.402777777777778E-3</v>
+      </c>
+      <c r="E102" s="92">
+        <f>SUM(D60:D102)</f>
+        <v>1.0073379629629633</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="str">
         <f>"总时长："&amp;TEXT(SUM(B:B)/1440+SUM(C:C)/86400,"[h]:mm:ss")</f>
         <v>总时长：59:26:28</v>
@@ -12106,6 +13038,1097 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28484A4-8D96-4893-8540-2AA12A87E9FD}">
+  <dimension ref="A1:F74"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="36.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="31" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="25" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>894</v>
+      </c>
+      <c r="B3">
+        <v>34</v>
+      </c>
+      <c r="C3">
+        <v>28</v>
+      </c>
+      <c r="D3" s="91">
+        <f t="shared" ref="D3:D34" si="0">IF(ISBLANK(C3),"",B3/1440+C3/86400)</f>
+        <v>2.3935185185185184E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>895</v>
+      </c>
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>15</v>
+      </c>
+      <c r="D4" s="91">
+        <f t="shared" si="0"/>
+        <v>1.7534722222222222E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>896</v>
+      </c>
+      <c r="B5">
+        <v>33</v>
+      </c>
+      <c r="C5">
+        <v>57</v>
+      </c>
+      <c r="D5" s="91">
+        <f t="shared" si="0"/>
+        <v>2.3576388888888886E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>897</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" s="91">
+        <f t="shared" si="0"/>
+        <v>8.4027777777777781E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>898</v>
+      </c>
+      <c r="B7">
+        <v>39</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7" s="91">
+        <f t="shared" si="0"/>
+        <v>2.7245370370370371E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>899</v>
+      </c>
+      <c r="B8">
+        <v>61</v>
+      </c>
+      <c r="C8">
+        <v>27</v>
+      </c>
+      <c r="D8" s="91">
+        <f t="shared" si="0"/>
+        <v>4.2673611111111114E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>900</v>
+      </c>
+      <c r="B9">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9" s="91">
+        <f t="shared" si="0"/>
+        <v>2.0509259259259262E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>901</v>
+      </c>
+      <c r="B10">
+        <v>37</v>
+      </c>
+      <c r="C10">
+        <v>29</v>
+      </c>
+      <c r="D10" s="91">
+        <f t="shared" si="0"/>
+        <v>2.6030092592592591E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>902</v>
+      </c>
+      <c r="B11">
+        <v>63</v>
+      </c>
+      <c r="C11">
+        <v>40</v>
+      </c>
+      <c r="D11" s="91">
+        <f t="shared" si="0"/>
+        <v>4.4212962962962961E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>903</v>
+      </c>
+      <c r="B12">
+        <v>56</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12" s="91">
+        <f t="shared" si="0"/>
+        <v>3.9004629629629632E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>904</v>
+      </c>
+      <c r="B13">
+        <v>34</v>
+      </c>
+      <c r="C13">
+        <v>32</v>
+      </c>
+      <c r="D13" s="91">
+        <f t="shared" si="0"/>
+        <v>2.3981481481481482E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>905</v>
+      </c>
+      <c r="B14">
+        <v>24</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+      <c r="D14" s="91">
+        <f t="shared" si="0"/>
+        <v>1.681712962962963E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>906</v>
+      </c>
+      <c r="B15">
+        <v>47</v>
+      </c>
+      <c r="C15">
+        <v>32</v>
+      </c>
+      <c r="D15" s="91">
+        <f t="shared" si="0"/>
+        <v>3.3009259259259259E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>907</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>22</v>
+      </c>
+      <c r="D16" s="91">
+        <f t="shared" si="0"/>
+        <v>1.136574074074074E-2</v>
+      </c>
+      <c r="E16" s="92">
+        <f>SUM(D3:D16)</f>
+        <v>0.35829861111111111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>908</v>
+      </c>
+      <c r="D17" s="91"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>909</v>
+      </c>
+      <c r="B18">
+        <v>20</v>
+      </c>
+      <c r="C18">
+        <v>46</v>
+      </c>
+      <c r="D18" s="91">
+        <f t="shared" si="0"/>
+        <v>1.4421296296296295E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>910</v>
+      </c>
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="C19">
+        <v>39</v>
+      </c>
+      <c r="D19" s="91">
+        <f t="shared" si="0"/>
+        <v>1.4340277777777776E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>911</v>
+      </c>
+      <c r="B20">
+        <v>66</v>
+      </c>
+      <c r="C20">
+        <v>35</v>
+      </c>
+      <c r="D20" s="91">
+        <f t="shared" si="0"/>
+        <v>4.6238425925925926E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>912</v>
+      </c>
+      <c r="B21">
+        <v>23</v>
+      </c>
+      <c r="C21">
+        <v>45</v>
+      </c>
+      <c r="D21" s="91">
+        <f t="shared" si="0"/>
+        <v>1.6493055555555556E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>913</v>
+      </c>
+      <c r="B22">
+        <v>40</v>
+      </c>
+      <c r="C22">
+        <v>52</v>
+      </c>
+      <c r="D22" s="91">
+        <f t="shared" si="0"/>
+        <v>2.837962962962963E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>914</v>
+      </c>
+      <c r="B23">
+        <v>24</v>
+      </c>
+      <c r="C23">
+        <v>34</v>
+      </c>
+      <c r="D23" s="91">
+        <f t="shared" si="0"/>
+        <v>1.7060185185185185E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>915</v>
+      </c>
+      <c r="B24">
+        <v>57</v>
+      </c>
+      <c r="C24">
+        <v>53</v>
+      </c>
+      <c r="D24" s="91">
+        <f t="shared" si="0"/>
+        <v>4.0196759259259258E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>916</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>52</v>
+      </c>
+      <c r="D25" s="91">
+        <f t="shared" si="0"/>
+        <v>5.4629629629629629E-3</v>
+      </c>
+      <c r="E25" s="92">
+        <f>SUM(D18:D25)</f>
+        <v>0.18259259259259258</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="25" t="s">
+        <v>917</v>
+      </c>
+      <c r="D26" s="91"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>918</v>
+      </c>
+      <c r="B27">
+        <v>38</v>
+      </c>
+      <c r="C27">
+        <v>22</v>
+      </c>
+      <c r="D27" s="91">
+        <f t="shared" si="0"/>
+        <v>2.6643518518518518E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>919</v>
+      </c>
+      <c r="B28">
+        <v>13</v>
+      </c>
+      <c r="C28">
+        <v>22</v>
+      </c>
+      <c r="D28" s="91">
+        <f t="shared" si="0"/>
+        <v>9.2824074074074059E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>920</v>
+      </c>
+      <c r="B29">
+        <v>39</v>
+      </c>
+      <c r="C29">
+        <v>16</v>
+      </c>
+      <c r="D29" s="91">
+        <f t="shared" si="0"/>
+        <v>2.7268518518518518E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>921</v>
+      </c>
+      <c r="B30">
+        <v>41</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" s="91">
+        <f t="shared" si="0"/>
+        <v>2.8495370370370369E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>922</v>
+      </c>
+      <c r="B31">
+        <v>25</v>
+      </c>
+      <c r="C31">
+        <v>48</v>
+      </c>
+      <c r="D31" s="91">
+        <f t="shared" si="0"/>
+        <v>1.7916666666666668E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>923</v>
+      </c>
+      <c r="B32">
+        <v>37</v>
+      </c>
+      <c r="C32">
+        <v>36</v>
+      </c>
+      <c r="D32" s="91">
+        <f t="shared" si="0"/>
+        <v>2.6111111111111109E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>924</v>
+      </c>
+      <c r="B33">
+        <v>36</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33" s="91">
+        <f t="shared" si="0"/>
+        <v>2.5069444444444446E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>925</v>
+      </c>
+      <c r="B34">
+        <v>17</v>
+      </c>
+      <c r="C34">
+        <v>20</v>
+      </c>
+      <c r="D34" s="91">
+        <f t="shared" si="0"/>
+        <v>1.2037037037037037E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>926</v>
+      </c>
+      <c r="B35">
+        <v>43</v>
+      </c>
+      <c r="C35">
+        <v>59</v>
+      </c>
+      <c r="D35" s="91">
+        <f t="shared" ref="D35:D65" si="1">IF(ISBLANK(C35),"",B35/1440+C35/86400)</f>
+        <v>3.0543981481481484E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>927</v>
+      </c>
+      <c r="B36">
+        <v>58</v>
+      </c>
+      <c r="C36">
+        <v>9</v>
+      </c>
+      <c r="D36" s="91">
+        <f t="shared" si="1"/>
+        <v>4.0381944444444449E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>928</v>
+      </c>
+      <c r="B37">
+        <v>9</v>
+      </c>
+      <c r="C37">
+        <v>45</v>
+      </c>
+      <c r="D37" s="91">
+        <f t="shared" si="1"/>
+        <v>6.7708333333333336E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>929</v>
+      </c>
+      <c r="B38">
+        <v>31</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+      <c r="D38" s="91">
+        <f t="shared" si="1"/>
+        <v>2.1550925925925925E-2</v>
+      </c>
+      <c r="E38" s="92">
+        <f>SUM(D27:D38)</f>
+        <v>0.2720717592592593</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="25" t="s">
+        <v>930</v>
+      </c>
+      <c r="D39" s="91"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>931</v>
+      </c>
+      <c r="B40">
+        <v>33</v>
+      </c>
+      <c r="C40">
+        <v>37</v>
+      </c>
+      <c r="D40" s="91">
+        <f t="shared" si="1"/>
+        <v>2.3344907407407404E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>932</v>
+      </c>
+      <c r="B41">
+        <v>9</v>
+      </c>
+      <c r="C41">
+        <v>41</v>
+      </c>
+      <c r="D41" s="91">
+        <f t="shared" si="1"/>
+        <v>6.7245370370370375E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>933</v>
+      </c>
+      <c r="B42">
+        <v>25</v>
+      </c>
+      <c r="C42">
+        <v>49</v>
+      </c>
+      <c r="D42" s="91">
+        <f t="shared" si="1"/>
+        <v>1.7928240740740741E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>934</v>
+      </c>
+      <c r="B43">
+        <v>26</v>
+      </c>
+      <c r="C43">
+        <v>19</v>
+      </c>
+      <c r="D43" s="91">
+        <f t="shared" si="1"/>
+        <v>1.8275462962962962E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>935</v>
+      </c>
+      <c r="B44">
+        <v>43</v>
+      </c>
+      <c r="C44">
+        <v>20</v>
+      </c>
+      <c r="D44" s="91">
+        <f t="shared" si="1"/>
+        <v>3.0092592592592594E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>936</v>
+      </c>
+      <c r="B45">
+        <v>47</v>
+      </c>
+      <c r="C45">
+        <v>40</v>
+      </c>
+      <c r="D45" s="91">
+        <f t="shared" si="1"/>
+        <v>3.3101851851851855E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>937</v>
+      </c>
+      <c r="B46">
+        <v>50</v>
+      </c>
+      <c r="C46">
+        <v>8</v>
+      </c>
+      <c r="D46" s="91">
+        <f t="shared" si="1"/>
+        <v>3.4814814814814819E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>938</v>
+      </c>
+      <c r="B47">
+        <v>9</v>
+      </c>
+      <c r="C47">
+        <v>39</v>
+      </c>
+      <c r="D47" s="91">
+        <f t="shared" si="1"/>
+        <v>6.7013888888888895E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>939</v>
+      </c>
+      <c r="B48">
+        <v>16</v>
+      </c>
+      <c r="C48">
+        <v>48</v>
+      </c>
+      <c r="D48" s="91">
+        <f t="shared" si="1"/>
+        <v>1.1666666666666667E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>940</v>
+      </c>
+      <c r="B49">
+        <v>38</v>
+      </c>
+      <c r="C49">
+        <v>29</v>
+      </c>
+      <c r="D49" s="91">
+        <f t="shared" si="1"/>
+        <v>2.6724537037037036E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>941</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>45</v>
+      </c>
+      <c r="D50" s="91">
+        <f t="shared" si="1"/>
+        <v>6.076388888888889E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>942</v>
+      </c>
+      <c r="B51">
+        <v>43</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51" s="91">
+        <f t="shared" si="1"/>
+        <v>2.9861111111111113E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>943</v>
+      </c>
+      <c r="B52">
+        <v>31</v>
+      </c>
+      <c r="C52">
+        <v>22</v>
+      </c>
+      <c r="D52" s="91">
+        <f t="shared" si="1"/>
+        <v>2.1782407407407407E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>944</v>
+      </c>
+      <c r="B53">
+        <v>35</v>
+      </c>
+      <c r="C53">
+        <v>7</v>
+      </c>
+      <c r="D53" s="91">
+        <f t="shared" si="1"/>
+        <v>2.4386574074074074E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>945</v>
+      </c>
+      <c r="B54">
+        <v>58</v>
+      </c>
+      <c r="C54">
+        <v>10</v>
+      </c>
+      <c r="D54" s="91">
+        <f t="shared" si="1"/>
+        <v>4.0393518518518523E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>946</v>
+      </c>
+      <c r="B55">
+        <v>15</v>
+      </c>
+      <c r="C55">
+        <v>49</v>
+      </c>
+      <c r="D55" s="91">
+        <f t="shared" si="1"/>
+        <v>1.0983796296296295E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>947</v>
+      </c>
+      <c r="B56">
+        <v>61</v>
+      </c>
+      <c r="C56">
+        <v>58</v>
+      </c>
+      <c r="D56" s="91">
+        <f t="shared" si="1"/>
+        <v>4.3032407407407408E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>948</v>
+      </c>
+      <c r="B57">
+        <v>24</v>
+      </c>
+      <c r="C57">
+        <v>8</v>
+      </c>
+      <c r="D57" s="91">
+        <f t="shared" si="1"/>
+        <v>1.6759259259259258E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>949</v>
+      </c>
+      <c r="B58">
+        <v>27</v>
+      </c>
+      <c r="C58">
+        <v>34</v>
+      </c>
+      <c r="D58" s="91">
+        <f t="shared" si="1"/>
+        <v>1.9143518518518518E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>950</v>
+      </c>
+      <c r="B59">
+        <v>13</v>
+      </c>
+      <c r="C59">
+        <v>58</v>
+      </c>
+      <c r="D59" s="91">
+        <f t="shared" si="1"/>
+        <v>9.6990740740740735E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>951</v>
+      </c>
+      <c r="B60">
+        <v>22</v>
+      </c>
+      <c r="C60">
+        <v>17</v>
+      </c>
+      <c r="D60" s="91">
+        <f t="shared" si="1"/>
+        <v>1.5474537037037037E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>952</v>
+      </c>
+      <c r="B61">
+        <v>20</v>
+      </c>
+      <c r="C61">
+        <v>28</v>
+      </c>
+      <c r="D61" s="91">
+        <f t="shared" si="1"/>
+        <v>1.4212962962962962E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>953</v>
+      </c>
+      <c r="B62">
+        <v>20</v>
+      </c>
+      <c r="C62">
+        <v>11</v>
+      </c>
+      <c r="D62" s="91">
+        <f t="shared" si="1"/>
+        <v>1.4016203703703703E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>954</v>
+      </c>
+      <c r="B63">
+        <v>34</v>
+      </c>
+      <c r="C63">
+        <v>31</v>
+      </c>
+      <c r="D63" s="91">
+        <f t="shared" si="1"/>
+        <v>2.3969907407407405E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>955</v>
+      </c>
+      <c r="B64">
+        <v>47</v>
+      </c>
+      <c r="C64">
+        <v>38</v>
+      </c>
+      <c r="D64" s="91">
+        <f t="shared" si="1"/>
+        <v>3.3078703703703707E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>956</v>
+      </c>
+      <c r="B65">
+        <v>34</v>
+      </c>
+      <c r="C65">
+        <v>35</v>
+      </c>
+      <c r="D65" s="91">
+        <f t="shared" si="1"/>
+        <v>2.4016203703703703E-2</v>
+      </c>
+      <c r="E65" s="92">
+        <f>SUM(D40:D65)</f>
+        <v>0.55626157407407417</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" s="25" t="s">
+        <v>957</v>
+      </c>
+      <c r="D66" s="91"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>958</v>
+      </c>
+      <c r="B67">
+        <v>42</v>
+      </c>
+      <c r="C67">
+        <v>39</v>
+      </c>
+      <c r="D67" s="91">
+        <f t="shared" ref="D67:D73" si="2">IF(ISBLANK(C67),"",B67/1440+C67/86400)</f>
+        <v>2.9618055555555557E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>959</v>
+      </c>
+      <c r="B68">
+        <v>21</v>
+      </c>
+      <c r="C68">
+        <v>35</v>
+      </c>
+      <c r="D68" s="91">
+        <f t="shared" si="2"/>
+        <v>1.4988425925925926E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>960</v>
+      </c>
+      <c r="B69">
+        <v>46</v>
+      </c>
+      <c r="C69">
+        <v>4</v>
+      </c>
+      <c r="D69" s="91">
+        <f t="shared" si="2"/>
+        <v>3.1990740740740736E-2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>961</v>
+      </c>
+      <c r="B70">
+        <v>34</v>
+      </c>
+      <c r="C70">
+        <v>46</v>
+      </c>
+      <c r="D70" s="91">
+        <f t="shared" si="2"/>
+        <v>2.4143518518518519E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>962</v>
+      </c>
+      <c r="B71">
+        <v>31</v>
+      </c>
+      <c r="C71">
+        <v>8</v>
+      </c>
+      <c r="D71" s="91">
+        <f t="shared" si="2"/>
+        <v>2.162037037037037E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>963</v>
+      </c>
+      <c r="B72">
+        <v>14</v>
+      </c>
+      <c r="C72">
+        <v>41</v>
+      </c>
+      <c r="D72" s="91">
+        <f t="shared" si="2"/>
+        <v>1.019675925925926E-2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>964</v>
+      </c>
+      <c r="B73">
+        <v>50</v>
+      </c>
+      <c r="C73">
+        <v>57</v>
+      </c>
+      <c r="D73" s="91">
+        <f t="shared" si="2"/>
+        <v>3.5381944444444445E-2</v>
+      </c>
+      <c r="E73" s="92">
+        <f>SUM(D67:D73)</f>
+        <v>0.16793981481481482</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" s="9" t="str">
+        <f>"总时长："&amp;TEXT(SUM(B:B)/1440+SUM(C:C)/86400,"[h]:mm:ss")</f>
+        <v>总时长：36:53:31</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08238647-BBF6-4C2C-B188-33145A4D65D9}">
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -12384,7 +14407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E16794E-744F-4D5E-88D3-DF76CD9771EA}">
   <sheetPr codeName="Sheet19"/>
   <dimension ref="A1:F51"/>
@@ -12923,805 +14946,6 @@
       <c r="A51" s="9" t="str">
         <f>"总时长："&amp;TEXT(SUM(B:B)/1440+SUM(C:C)/86400,"[h]:mm:ss")</f>
         <v>总时长：26:54:20</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28484A4-8D96-4893-8540-2AA12A87E9FD}">
-  <dimension ref="A1:F74"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="36.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="31" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>894</v>
-      </c>
-      <c r="B3">
-        <v>34</v>
-      </c>
-      <c r="C3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>895</v>
-      </c>
-      <c r="B4">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>896</v>
-      </c>
-      <c r="B5">
-        <v>33</v>
-      </c>
-      <c r="C5">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>897</v>
-      </c>
-      <c r="B6">
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>898</v>
-      </c>
-      <c r="B7">
-        <v>39</v>
-      </c>
-      <c r="C7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>899</v>
-      </c>
-      <c r="B8">
-        <v>61</v>
-      </c>
-      <c r="C8">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>900</v>
-      </c>
-      <c r="B9">
-        <v>29</v>
-      </c>
-      <c r="C9">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>901</v>
-      </c>
-      <c r="B10">
-        <v>37</v>
-      </c>
-      <c r="C10">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>902</v>
-      </c>
-      <c r="B11">
-        <v>63</v>
-      </c>
-      <c r="C11">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>903</v>
-      </c>
-      <c r="B12">
-        <v>56</v>
-      </c>
-      <c r="C12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>904</v>
-      </c>
-      <c r="B13">
-        <v>34</v>
-      </c>
-      <c r="C13">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>905</v>
-      </c>
-      <c r="B14">
-        <v>24</v>
-      </c>
-      <c r="C14">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>906</v>
-      </c>
-      <c r="B15">
-        <v>47</v>
-      </c>
-      <c r="C15">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>907</v>
-      </c>
-      <c r="B16">
-        <v>16</v>
-      </c>
-      <c r="C16">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>909</v>
-      </c>
-      <c r="B18">
-        <v>20</v>
-      </c>
-      <c r="C18">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>910</v>
-      </c>
-      <c r="B19">
-        <v>20</v>
-      </c>
-      <c r="C19">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>911</v>
-      </c>
-      <c r="B20">
-        <v>66</v>
-      </c>
-      <c r="C20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>912</v>
-      </c>
-      <c r="B21">
-        <v>23</v>
-      </c>
-      <c r="C21">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>913</v>
-      </c>
-      <c r="B22">
-        <v>40</v>
-      </c>
-      <c r="C22">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>914</v>
-      </c>
-      <c r="B23">
-        <v>24</v>
-      </c>
-      <c r="C23">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>915</v>
-      </c>
-      <c r="B24">
-        <v>57</v>
-      </c>
-      <c r="C24">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>916</v>
-      </c>
-      <c r="B25">
-        <v>7</v>
-      </c>
-      <c r="C25">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="25" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>918</v>
-      </c>
-      <c r="B27">
-        <v>38</v>
-      </c>
-      <c r="C27">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>919</v>
-      </c>
-      <c r="B28">
-        <v>13</v>
-      </c>
-      <c r="C28">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>920</v>
-      </c>
-      <c r="B29">
-        <v>39</v>
-      </c>
-      <c r="C29">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>921</v>
-      </c>
-      <c r="B30">
-        <v>41</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>922</v>
-      </c>
-      <c r="B31">
-        <v>25</v>
-      </c>
-      <c r="C31">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>923</v>
-      </c>
-      <c r="B32">
-        <v>37</v>
-      </c>
-      <c r="C32">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>924</v>
-      </c>
-      <c r="B33">
-        <v>36</v>
-      </c>
-      <c r="C33">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>925</v>
-      </c>
-      <c r="B34">
-        <v>17</v>
-      </c>
-      <c r="C34">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>926</v>
-      </c>
-      <c r="B35">
-        <v>43</v>
-      </c>
-      <c r="C35">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>927</v>
-      </c>
-      <c r="B36">
-        <v>58</v>
-      </c>
-      <c r="C36">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>928</v>
-      </c>
-      <c r="B37">
-        <v>9</v>
-      </c>
-      <c r="C37">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>929</v>
-      </c>
-      <c r="B38">
-        <v>31</v>
-      </c>
-      <c r="C38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="25" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>931</v>
-      </c>
-      <c r="B40">
-        <v>33</v>
-      </c>
-      <c r="C40">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>932</v>
-      </c>
-      <c r="B41">
-        <v>9</v>
-      </c>
-      <c r="C41">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>933</v>
-      </c>
-      <c r="B42">
-        <v>25</v>
-      </c>
-      <c r="C42">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>934</v>
-      </c>
-      <c r="B43">
-        <v>26</v>
-      </c>
-      <c r="C43">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>935</v>
-      </c>
-      <c r="B44">
-        <v>43</v>
-      </c>
-      <c r="C44">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>936</v>
-      </c>
-      <c r="B45">
-        <v>47</v>
-      </c>
-      <c r="C45">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>937</v>
-      </c>
-      <c r="B46">
-        <v>50</v>
-      </c>
-      <c r="C46">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>938</v>
-      </c>
-      <c r="B47">
-        <v>9</v>
-      </c>
-      <c r="C47">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>939</v>
-      </c>
-      <c r="B48">
-        <v>16</v>
-      </c>
-      <c r="C48">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>940</v>
-      </c>
-      <c r="B49">
-        <v>38</v>
-      </c>
-      <c r="C49">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>941</v>
-      </c>
-      <c r="B50">
-        <v>8</v>
-      </c>
-      <c r="C50">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>942</v>
-      </c>
-      <c r="B51">
-        <v>43</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>943</v>
-      </c>
-      <c r="B52">
-        <v>31</v>
-      </c>
-      <c r="C52">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>944</v>
-      </c>
-      <c r="B53">
-        <v>35</v>
-      </c>
-      <c r="C53">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>945</v>
-      </c>
-      <c r="B54">
-        <v>58</v>
-      </c>
-      <c r="C54">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>946</v>
-      </c>
-      <c r="B55">
-        <v>15</v>
-      </c>
-      <c r="C55">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>947</v>
-      </c>
-      <c r="B56">
-        <v>61</v>
-      </c>
-      <c r="C56">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>948</v>
-      </c>
-      <c r="B57">
-        <v>24</v>
-      </c>
-      <c r="C57">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>949</v>
-      </c>
-      <c r="B58">
-        <v>27</v>
-      </c>
-      <c r="C58">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>950</v>
-      </c>
-      <c r="B59">
-        <v>13</v>
-      </c>
-      <c r="C59">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>951</v>
-      </c>
-      <c r="B60">
-        <v>22</v>
-      </c>
-      <c r="C60">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>952</v>
-      </c>
-      <c r="B61">
-        <v>20</v>
-      </c>
-      <c r="C61">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>953</v>
-      </c>
-      <c r="B62">
-        <v>20</v>
-      </c>
-      <c r="C62">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>954</v>
-      </c>
-      <c r="B63">
-        <v>34</v>
-      </c>
-      <c r="C63">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>955</v>
-      </c>
-      <c r="B64">
-        <v>47</v>
-      </c>
-      <c r="C64">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>956</v>
-      </c>
-      <c r="B65">
-        <v>34</v>
-      </c>
-      <c r="C65">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="25" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>958</v>
-      </c>
-      <c r="B67">
-        <v>42</v>
-      </c>
-      <c r="C67">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>959</v>
-      </c>
-      <c r="B68">
-        <v>21</v>
-      </c>
-      <c r="C68">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>960</v>
-      </c>
-      <c r="B69">
-        <v>46</v>
-      </c>
-      <c r="C69">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>961</v>
-      </c>
-      <c r="B70">
-        <v>34</v>
-      </c>
-      <c r="C70">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>962</v>
-      </c>
-      <c r="B71">
-        <v>31</v>
-      </c>
-      <c r="C71">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>963</v>
-      </c>
-      <c r="B72">
-        <v>14</v>
-      </c>
-      <c r="C72">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>964</v>
-      </c>
-      <c r="B73">
-        <v>50</v>
-      </c>
-      <c r="C73">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="9" t="str">
-        <f>"总时长："&amp;TEXT(SUM(B:B)/1440+SUM(C:C)/86400,"[h]:mm:ss")</f>
-        <v>总时长：36:53:31</v>
       </c>
     </row>
   </sheetData>

--- a/assets/contents.xlsx
+++ b/assets/contents.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Courses\duyiFe\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{247F28C5-7872-4569-826A-4FEAF4C2455D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B11DB3-9360-4953-A645-E14953843564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="1860" windowWidth="21600" windowHeight="11820" tabRatio="722" firstSheet="16" activeTab="20" xr2:uid="{977D219B-3D5A-4B74-BC43-A61DD328A31A}"/>
+    <workbookView xWindow="1845" yWindow="1860" windowWidth="21600" windowHeight="11820" tabRatio="722" firstSheet="17" activeTab="20" xr2:uid="{977D219B-3D5A-4B74-BC43-A61DD328A31A}"/>
   </bookViews>
   <sheets>
     <sheet name="1HTML_scratch" sheetId="9" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="1204">
   <si>
     <t>1. 环境准备</t>
   </si>
@@ -4001,7 +4001,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4279,6 +4279,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11525,6 +11534,9 @@
         <v>37</v>
       </c>
       <c r="D1" s="15" t="s">
+        <v>892</v>
+      </c>
+      <c r="E1" s="94" t="s">
         <v>53</v>
       </c>
       <c r="F1" s="31" t="s">
@@ -11535,46 +11547,53 @@
       <c r="A2" s="25" t="s">
         <v>764</v>
       </c>
+      <c r="E2" s="45"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="A3" s="63" t="s">
         <v>765</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="57">
         <v>13</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="57">
         <v>10</v>
       </c>
-      <c r="D3" s="91">
+      <c r="D3" s="95">
         <f t="shared" ref="D3:D34" si="0">B3/1440+C3/86400</f>
         <v>9.1435185185185178E-3</v>
       </c>
+      <c r="E3" s="45">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="A4" s="57" t="s">
         <v>766</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="57">
         <v>15</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="57">
         <v>24</v>
       </c>
-      <c r="D4" s="91">
+      <c r="D4" s="95">
         <f t="shared" si="0"/>
         <v>1.0694444444444444E-2</v>
       </c>
-      <c r="E4" s="92">
-        <f>SUM(D3:D4)</f>
-        <v>1.983796296296296E-2</v>
+      <c r="E4" s="45">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>767</v>
       </c>
-      <c r="D5" s="91"/>
+      <c r="D5" s="93">
+        <f>SUM(D3:D4)</f>
+        <v>1.983796296296296E-2</v>
+      </c>
+      <c r="E5" s="45"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -11590,6 +11609,7 @@
         <f t="shared" si="0"/>
         <v>1.4895833333333334E-2</v>
       </c>
+      <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
@@ -11605,6 +11625,7 @@
         <f t="shared" si="0"/>
         <v>2.3206018518518518E-2</v>
       </c>
+      <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="36" t="s">
@@ -11620,6 +11641,7 @@
         <f t="shared" si="0"/>
         <v>2.8067129629629629E-2</v>
       </c>
+      <c r="E8" s="45"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="36" t="s">
@@ -11635,6 +11657,7 @@
         <f t="shared" si="0"/>
         <v>2.1979166666666668E-2</v>
       </c>
+      <c r="E9" s="45"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -11650,6 +11673,7 @@
         <f t="shared" si="0"/>
         <v>3.4942129629629629E-2</v>
       </c>
+      <c r="E10" s="45"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -11665,6 +11689,7 @@
         <f t="shared" si="0"/>
         <v>2.1331018518518517E-2</v>
       </c>
+      <c r="E11" s="45"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -11680,6 +11705,7 @@
         <f t="shared" si="0"/>
         <v>3.2650462962962964E-2</v>
       </c>
+      <c r="E12" s="45"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -11695,6 +11721,7 @@
         <f t="shared" si="0"/>
         <v>2.3715277777777776E-2</v>
       </c>
+      <c r="E13" s="45"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -11710,6 +11737,7 @@
         <f t="shared" si="0"/>
         <v>3.2511574074074075E-2</v>
       </c>
+      <c r="E14" s="45"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -11725,6 +11753,7 @@
         <f t="shared" si="0"/>
         <v>2.8599537037037038E-2</v>
       </c>
+      <c r="E15" s="45"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -11740,8 +11769,9 @@
         <f t="shared" si="0"/>
         <v>3.4768518518518518E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E16" s="45"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>779</v>
       </c>
@@ -11755,8 +11785,9 @@
         <f t="shared" si="0"/>
         <v>2.3842592592592592E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E17" s="45"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>780</v>
       </c>
@@ -11770,8 +11801,9 @@
         <f t="shared" si="0"/>
         <v>2.2881944444444444E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E18" s="45"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>781</v>
       </c>
@@ -11785,8 +11817,9 @@
         <f t="shared" si="0"/>
         <v>3.7928240740740742E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E19" s="45"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>782</v>
       </c>
@@ -11800,8 +11833,9 @@
         <f t="shared" si="0"/>
         <v>2.315972222222222E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E20" s="45"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>783</v>
       </c>
@@ -11815,8 +11849,9 @@
         <f t="shared" si="0"/>
         <v>2.1111111111111108E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E21" s="45"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>784</v>
       </c>
@@ -11830,8 +11865,9 @@
         <f t="shared" si="0"/>
         <v>2.2083333333333333E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" s="45"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>785</v>
       </c>
@@ -11845,8 +11881,9 @@
         <f t="shared" si="0"/>
         <v>2.7812499999999997E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23" s="45"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>786</v>
       </c>
@@ -11860,8 +11897,9 @@
         <f t="shared" si="0"/>
         <v>3.0162037037037039E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24" s="45"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>787</v>
       </c>
@@ -11875,8 +11913,9 @@
         <f t="shared" si="0"/>
         <v>2.3032407407407404E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E25" s="45"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>788</v>
       </c>
@@ -11890,8 +11929,9 @@
         <f t="shared" si="0"/>
         <v>2.3344907407407404E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26" s="45"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>789</v>
       </c>
@@ -11905,8 +11945,9 @@
         <f t="shared" si="0"/>
         <v>2.9675925925925925E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E27" s="45"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>790</v>
       </c>
@@ -11920,8 +11961,9 @@
         <f t="shared" si="0"/>
         <v>1.699074074074074E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E28" s="45"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>791</v>
       </c>
@@ -11935,8 +11977,9 @@
         <f t="shared" si="0"/>
         <v>2.4791666666666667E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29" s="45"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>792</v>
       </c>
@@ -11950,8 +11993,9 @@
         <f t="shared" si="0"/>
         <v>3.0462962962962966E-2</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E30" s="45"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>793</v>
       </c>
@@ -11965,8 +12009,9 @@
         <f t="shared" si="0"/>
         <v>3.3402777777777774E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E31" s="45"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>794</v>
       </c>
@@ -11980,6 +12025,7 @@
         <f t="shared" si="0"/>
         <v>2.0937499999999998E-2</v>
       </c>
+      <c r="E32" s="45"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -11995,6 +12041,7 @@
         <f t="shared" si="0"/>
         <v>1.8368055555555554E-2</v>
       </c>
+      <c r="E33" s="45"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
@@ -12010,6 +12057,7 @@
         <f t="shared" si="0"/>
         <v>2.7708333333333335E-2</v>
       </c>
+      <c r="E34" s="45"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -12025,16 +12073,17 @@
         <f t="shared" ref="D35:D66" si="1">B35/1440+C35/86400</f>
         <v>4.355324074074074E-2</v>
       </c>
-      <c r="E35" s="92">
-        <f>SUM(D6:D35)</f>
-        <v>0.7979166666666665</v>
-      </c>
+      <c r="E35" s="45"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
         <v>798</v>
       </c>
-      <c r="D36" s="91"/>
+      <c r="D36" s="93">
+        <f>SUM(D6:D35)</f>
+        <v>0.7979166666666665</v>
+      </c>
+      <c r="E36" s="45"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -12050,6 +12099,7 @@
         <f t="shared" si="1"/>
         <v>1.275462962962963E-2</v>
       </c>
+      <c r="E37" s="45"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -12065,6 +12115,7 @@
         <f t="shared" si="1"/>
         <v>6.0879629629629631E-2</v>
       </c>
+      <c r="E38" s="45"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
@@ -12080,6 +12131,7 @@
         <f t="shared" si="1"/>
         <v>4.1018518518518517E-2</v>
       </c>
+      <c r="E39" s="45"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
@@ -12095,6 +12147,7 @@
         <f t="shared" si="1"/>
         <v>1.6724537037037038E-2</v>
       </c>
+      <c r="E40" s="45"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
@@ -12110,6 +12163,7 @@
         <f t="shared" si="1"/>
         <v>4.1585648148148149E-2</v>
       </c>
+      <c r="E41" s="45"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
@@ -12125,6 +12179,7 @@
         <f t="shared" si="1"/>
         <v>3.6249999999999998E-2</v>
       </c>
+      <c r="E42" s="45"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -12140,6 +12195,7 @@
         <f t="shared" si="1"/>
         <v>3.6932870370370373E-2</v>
       </c>
+      <c r="E43" s="45"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
@@ -12155,6 +12211,7 @@
         <f t="shared" si="1"/>
         <v>2.841435185185185E-2</v>
       </c>
+      <c r="E44" s="45"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
@@ -12170,6 +12227,7 @@
         <f t="shared" si="1"/>
         <v>3.8263888888888889E-2</v>
       </c>
+      <c r="E45" s="45"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
@@ -12185,6 +12243,7 @@
         <f t="shared" si="1"/>
         <v>3.0925925925925926E-2</v>
       </c>
+      <c r="E46" s="45"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
@@ -12200,6 +12259,7 @@
         <f t="shared" si="1"/>
         <v>3.5208333333333335E-2</v>
       </c>
+      <c r="E47" s="45"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
@@ -12215,6 +12275,7 @@
         <f t="shared" si="1"/>
         <v>3.4050925925925922E-2</v>
       </c>
+      <c r="E48" s="45"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
@@ -12230,6 +12291,7 @@
         <f t="shared" si="1"/>
         <v>1.849537037037037E-2</v>
       </c>
+      <c r="E49" s="45"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
@@ -12245,6 +12307,7 @@
         <f t="shared" si="1"/>
         <v>1.7372685185185185E-2</v>
       </c>
+      <c r="E50" s="45"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
@@ -12260,6 +12323,7 @@
         <f t="shared" si="1"/>
         <v>1.2650462962962964E-2</v>
       </c>
+      <c r="E51" s="45"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
@@ -12275,6 +12339,7 @@
         <f t="shared" si="1"/>
         <v>2.2280092592592594E-2</v>
       </c>
+      <c r="E52" s="45"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
@@ -12290,6 +12355,7 @@
         <f t="shared" si="1"/>
         <v>2.5671296296296296E-2</v>
       </c>
+      <c r="E53" s="45"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
@@ -12305,6 +12371,7 @@
         <f t="shared" si="1"/>
         <v>4.3564814814814813E-2</v>
       </c>
+      <c r="E54" s="45"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
@@ -12320,6 +12387,7 @@
         <f t="shared" si="1"/>
         <v>2.6585648148148146E-2</v>
       </c>
+      <c r="E55" s="45"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
@@ -12335,6 +12403,7 @@
         <f t="shared" si="1"/>
         <v>1.7905092592592594E-2</v>
       </c>
+      <c r="E56" s="45"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
@@ -12350,6 +12419,7 @@
         <f t="shared" si="1"/>
         <v>2.3113425925925923E-2</v>
       </c>
+      <c r="E57" s="45"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
@@ -12365,16 +12435,17 @@
         <f t="shared" si="1"/>
         <v>3.097222222222222E-2</v>
       </c>
-      <c r="E58" s="92">
-        <f>SUM(D37:D58)</f>
-        <v>0.65162037037037013</v>
-      </c>
+      <c r="E58" s="45"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59" s="25" t="s">
         <v>821</v>
       </c>
-      <c r="D59" s="91"/>
+      <c r="D59" s="93">
+        <f>SUM(D37:D58)</f>
+        <v>0.65162037037037013</v>
+      </c>
+      <c r="E59" s="45"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
@@ -12390,6 +12461,7 @@
         <f t="shared" si="1"/>
         <v>4.2708333333333331E-3</v>
       </c>
+      <c r="E60" s="45"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
@@ -12405,6 +12477,7 @@
         <f t="shared" si="1"/>
         <v>1.2916666666666667E-2</v>
       </c>
+      <c r="E61" s="45"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
@@ -12420,6 +12493,7 @@
         <f t="shared" si="1"/>
         <v>2.2152777777777778E-2</v>
       </c>
+      <c r="E62" s="45"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
@@ -12435,6 +12509,7 @@
         <f t="shared" si="1"/>
         <v>2.7106481481481481E-2</v>
       </c>
+      <c r="E63" s="45"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
@@ -12450,8 +12525,9 @@
         <f t="shared" si="1"/>
         <v>2.6979166666666665E-2</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E64" s="45"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>826</v>
       </c>
@@ -12465,8 +12541,9 @@
         <f t="shared" si="1"/>
         <v>2.6481481481481481E-2</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E65" s="45"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>827</v>
       </c>
@@ -12480,8 +12557,9 @@
         <f t="shared" si="1"/>
         <v>4.5856481481481477E-2</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E66" s="45"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>828</v>
       </c>
@@ -12495,8 +12573,9 @@
         <f t="shared" ref="D67:D98" si="2">B67/1440+C67/86400</f>
         <v>1.7349537037037038E-2</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E67" s="45"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>829</v>
       </c>
@@ -12510,8 +12589,9 @@
         <f t="shared" si="2"/>
         <v>1.1620370370370371E-2</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E68" s="45"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>830</v>
       </c>
@@ -12525,8 +12605,9 @@
         <f t="shared" si="2"/>
         <v>1.1817129629629629E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E69" s="45"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>831</v>
       </c>
@@ -12540,8 +12621,9 @@
         <f t="shared" si="2"/>
         <v>1.7083333333333332E-2</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E70" s="45"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>832</v>
       </c>
@@ -12555,8 +12637,9 @@
         <f t="shared" si="2"/>
         <v>2.1921296296296296E-2</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E71" s="45"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>833</v>
       </c>
@@ -12570,8 +12653,9 @@
         <f t="shared" si="2"/>
         <v>1.5266203703703704E-2</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E72" s="45"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>834</v>
       </c>
@@ -12585,8 +12669,9 @@
         <f t="shared" si="2"/>
         <v>1.5150462962962963E-2</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E73" s="45"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>835</v>
       </c>
@@ -12600,8 +12685,9 @@
         <f t="shared" si="2"/>
         <v>1.4212962962962962E-2</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74" s="45"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>836</v>
       </c>
@@ -12615,8 +12701,9 @@
         <f t="shared" si="2"/>
         <v>2.0370370370370372E-2</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E75" s="45"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>837</v>
       </c>
@@ -12630,8 +12717,9 @@
         <f t="shared" si="2"/>
         <v>4.2546296296296297E-2</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E76" s="45"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>838</v>
       </c>
@@ -12645,8 +12733,9 @@
         <f t="shared" si="2"/>
         <v>1.4780092592592593E-2</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E77" s="45"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>839</v>
       </c>
@@ -12660,8 +12749,9 @@
         <f t="shared" si="2"/>
         <v>1.3599537037037037E-2</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E78" s="45"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>840</v>
       </c>
@@ -12675,8 +12765,9 @@
         <f t="shared" si="2"/>
         <v>4.7708333333333332E-2</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E79" s="45"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>841</v>
       </c>
@@ -12690,8 +12781,9 @@
         <f t="shared" si="2"/>
         <v>3.4444444444444444E-2</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E80" s="45"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>842</v>
       </c>
@@ -12705,8 +12797,9 @@
         <f t="shared" si="2"/>
         <v>2.027777777777778E-2</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E81" s="45"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>843</v>
       </c>
@@ -12720,8 +12813,9 @@
         <f t="shared" si="2"/>
         <v>3.9861111111111111E-2</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E82" s="45"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>844</v>
       </c>
@@ -12735,8 +12829,9 @@
         <f t="shared" si="2"/>
         <v>1.4270833333333333E-2</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E83" s="45"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>845</v>
       </c>
@@ -12750,8 +12845,9 @@
         <f t="shared" si="2"/>
         <v>3.9849537037037037E-2</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E84" s="45"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>846</v>
       </c>
@@ -12765,8 +12861,9 @@
         <f t="shared" si="2"/>
         <v>4.1585648148148149E-2</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E85" s="45"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>847</v>
       </c>
@@ -12780,8 +12877,9 @@
         <f t="shared" si="2"/>
         <v>3.740740740740741E-2</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E86" s="45"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>848</v>
       </c>
@@ -12795,8 +12893,9 @@
         <f t="shared" si="2"/>
         <v>2.0914351851851851E-2</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E87" s="45"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>849</v>
       </c>
@@ -12810,8 +12909,9 @@
         <f t="shared" si="2"/>
         <v>1.1354166666666667E-2</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E88" s="45"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>850</v>
       </c>
@@ -12825,8 +12925,9 @@
         <f t="shared" si="2"/>
         <v>1.1481481481481481E-2</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E89" s="45"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>851</v>
       </c>
@@ -12840,8 +12941,9 @@
         <f t="shared" si="2"/>
         <v>3.8090277777777778E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E90" s="45"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>852</v>
       </c>
@@ -12855,8 +12957,9 @@
         <f t="shared" si="2"/>
         <v>1.6597222222222222E-2</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E91" s="45"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>853</v>
       </c>
@@ -12870,8 +12973,9 @@
         <f t="shared" si="2"/>
         <v>3.0624999999999999E-2</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E92" s="45"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>854</v>
       </c>
@@ -12885,8 +12989,9 @@
         <f t="shared" si="2"/>
         <v>1.8402777777777775E-2</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E93" s="45"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>855</v>
       </c>
@@ -12900,8 +13005,9 @@
         <f t="shared" si="2"/>
         <v>4.4641203703703704E-2</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E94" s="45"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>856</v>
       </c>
@@ -12915,8 +13021,9 @@
         <f t="shared" si="2"/>
         <v>1.8310185185185183E-2</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E95" s="45"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>857</v>
       </c>
@@ -12930,6 +13037,7 @@
         <f t="shared" si="2"/>
         <v>3.0671296296296294E-2</v>
       </c>
+      <c r="E96" s="45"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
@@ -12945,6 +13053,7 @@
         <f t="shared" si="2"/>
         <v>2.1331018518518517E-2</v>
       </c>
+      <c r="E97" s="45"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
@@ -12960,6 +13069,7 @@
         <f t="shared" si="2"/>
         <v>3.2129629629629626E-2</v>
       </c>
+      <c r="E98" s="45"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
@@ -12975,6 +13085,7 @@
         <f t="shared" ref="D99:D102" si="3">B99/1440+C99/86400</f>
         <v>1.5555555555555555E-2</v>
       </c>
+      <c r="E99" s="45"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
@@ -12990,6 +13101,7 @@
         <f t="shared" si="3"/>
         <v>2.4097222222222221E-2</v>
       </c>
+      <c r="E100" s="45"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
@@ -13005,6 +13117,7 @@
         <f t="shared" si="3"/>
         <v>1.2847222222222223E-2</v>
       </c>
+      <c r="E101" s="45"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
@@ -13020,15 +13133,16 @@
         <f t="shared" si="3"/>
         <v>3.402777777777778E-3</v>
       </c>
-      <c r="E102" s="92">
-        <f>SUM(D60:D102)</f>
-        <v>1.0073379629629633</v>
-      </c>
+      <c r="E102" s="45"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="str">
         <f>"总时长："&amp;TEXT(SUM(B:B)/1440+SUM(C:C)/86400,"[h]:mm:ss")</f>
         <v>总时长：59:26:28</v>
+      </c>
+      <c r="D103" s="93">
+        <f>SUM(D60:D102)</f>
+        <v>1.0073379629629633</v>
       </c>
     </row>
   </sheetData>

--- a/assets/contents.xlsx
+++ b/assets/contents.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Courses\duyiFe\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Courses\duyiFe\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B11DB3-9360-4953-A645-E14953843564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B2F3438-FE93-4278-8D75-EE6FCF7E27BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1845" yWindow="1860" windowWidth="21600" windowHeight="11820" tabRatio="722" firstSheet="17" activeTab="20" xr2:uid="{977D219B-3D5A-4B74-BC43-A61DD328A31A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="722" firstSheet="17" activeTab="20" xr2:uid="{977D219B-3D5A-4B74-BC43-A61DD328A31A}"/>
   </bookViews>
   <sheets>
     <sheet name="1HTML_scratch" sheetId="9" r:id="rId1"/>
@@ -42,29 +42,19 @@
     <sheet name="TS_pro" sheetId="29" r:id="rId27"/>
     <sheet name="Echarts" sheetId="20" r:id="rId28"/>
     <sheet name="BPMN" sheetId="22" r:id="rId29"/>
+    <sheet name="Git" sheetId="31" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="1204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1419" uniqueCount="1228">
   <si>
     <t>1. 环境准备</t>
   </si>
@@ -3735,6 +3725,88 @@
   </si>
   <si>
     <t>10 11 12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. git的安装和配置</t>
+  </si>
+  <si>
+    <t>2. 暂存和提交</t>
+  </si>
+  <si>
+    <t>3. 分支管理</t>
+  </si>
+  <si>
+    <t>4. 多账号SSH配置规范</t>
+  </si>
+  <si>
+    <t>5. 远程分支的同步</t>
+  </si>
+  <si>
+    <t>6. github flow - 完整流程</t>
+  </si>
+  <si>
+    <t>7. github flow - 协作者和陌生人</t>
+  </si>
+  <si>
+    <t>8. github flow - 冲突变基处理</t>
+  </si>
+  <si>
+    <t>9. github flow - cherry-pick</t>
+  </si>
+  <si>
+    <t>10. github flow - 工作流</t>
+  </si>
+  <si>
+    <t>11. github flow - tag和release</t>
+  </si>
+  <si>
+    <t>12. gitlab flow</t>
+  </si>
+  <si>
+    <t>13. 阿里云效流水线</t>
+  </si>
+  <si>
+    <t>14. worktree</t>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>computed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学习imooc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5 7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10 11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>element-plus/ant-design-vue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14 15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>整理笔记</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>19 20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20 21</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3742,8 +3814,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="hh:mm:ss"/>
+    <numFmt numFmtId="177" formatCode="yy\-mm\-dd\ hh:mm"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -3809,6 +3882,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -3857,6 +3931,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -4001,7 +4076,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4284,10 +4359,22 @@
     <xf numFmtId="46" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="21" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="46" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11517,13 +11604,14 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A6EF9A4-06A0-4B42-AB44-860D68BC6616}">
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>35</v>
       </c>
@@ -11539,17 +11627,24 @@
       <c r="E1" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="94" t="s">
+        <v>1218</v>
+      </c>
+      <c r="G1" s="31" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
         <v>764</v>
       </c>
+      <c r="C2" s="96">
+        <f>SUM(D3:D4)</f>
+        <v>1.983796296296296E-2</v>
+      </c>
       <c r="E2" s="45"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="63" t="s">
         <v>765</v>
       </c>
@@ -11560,14 +11655,17 @@
         <v>10</v>
       </c>
       <c r="D3" s="95">
-        <f t="shared" ref="D3:D34" si="0">B3/1440+C3/86400</f>
+        <f t="shared" ref="D3:D66" si="0">B3/1440+C3/86400</f>
         <v>9.1435185185185178E-3</v>
       </c>
       <c r="E3" s="45">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G3" s="97">
+        <v>45400.447916666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="57" t="s">
         <v>766</v>
       </c>
@@ -11584,886 +11682,1177 @@
       <c r="E4" s="45">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G4" s="97">
+        <v>45400.467361111114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="25" t="s">
         <v>767</v>
       </c>
-      <c r="D5" s="93">
-        <f>SUM(D3:D4)</f>
-        <v>1.983796296296296E-2</v>
+      <c r="C5" s="93">
+        <f>SUM(D6:D35)</f>
+        <v>0.7979166666666665</v>
       </c>
       <c r="E5" s="45"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="G5" s="97"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="63" t="s">
         <v>768</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="57">
         <v>21</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="57">
         <v>27</v>
       </c>
-      <c r="D6" s="91">
+      <c r="D6" s="95">
         <f t="shared" si="0"/>
         <v>1.4895833333333334E-2</v>
       </c>
-      <c r="E6" s="45"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="36" t="s">
+      <c r="E6" s="45">
+        <v>1</v>
+      </c>
+      <c r="G6" s="97">
+        <v>45401.628472222219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="89" t="s">
         <v>769</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="57">
         <v>33</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="57">
         <v>25</v>
       </c>
-      <c r="D7" s="91">
+      <c r="D7" s="95">
         <f t="shared" si="0"/>
         <v>2.3206018518518518E-2</v>
       </c>
-      <c r="E7" s="45"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="36" t="s">
+      <c r="E7" s="45">
+        <v>1</v>
+      </c>
+      <c r="G7" s="97">
+        <v>45401.431944444441</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="89" t="s">
         <v>770</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="57">
         <v>40</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="57">
         <v>25</v>
       </c>
-      <c r="D8" s="91">
+      <c r="D8" s="95">
         <f t="shared" si="0"/>
         <v>2.8067129629629629E-2</v>
       </c>
-      <c r="E8" s="45"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="36" t="s">
+      <c r="E8" s="45">
+        <v>2</v>
+      </c>
+      <c r="G8" s="97">
+        <v>45401.472222222219</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="89" t="s">
         <v>771</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="57">
         <v>31</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="57">
         <v>39</v>
       </c>
-      <c r="D9" s="91">
+      <c r="D9" s="95">
         <f t="shared" si="0"/>
         <v>2.1979166666666668E-2</v>
       </c>
-      <c r="E9" s="45"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="E9" s="45">
+        <v>2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G9" s="97">
+        <v>45401.576388888891</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="57" t="s">
         <v>772</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="57">
         <v>50</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="57">
         <v>19</v>
       </c>
-      <c r="D10" s="91">
+      <c r="D10" s="95">
         <f t="shared" si="0"/>
         <v>3.4942129629629629E-2</v>
       </c>
-      <c r="E10" s="45"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="E10" s="45">
+        <v>2</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1182</v>
+      </c>
+      <c r="G10" s="97">
+        <v>45448.522222222222</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="63" t="s">
         <v>773</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="57">
         <v>30</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="57">
         <v>43</v>
       </c>
-      <c r="D11" s="91">
+      <c r="D11" s="95">
         <f t="shared" si="0"/>
         <v>2.1331018518518517E-2</v>
       </c>
-      <c r="E11" s="45"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="E11" s="45">
+        <v>2</v>
+      </c>
+      <c r="G11" s="97">
+        <v>45448.584722222222</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="57" t="s">
         <v>774</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="57">
         <v>47</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="57">
         <v>1</v>
       </c>
-      <c r="D12" s="91">
+      <c r="D12" s="95">
         <f t="shared" si="0"/>
         <v>3.2650462962962964E-2</v>
       </c>
-      <c r="E12" s="45"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="E12" s="45">
+        <v>2</v>
+      </c>
+      <c r="G12" s="97">
+        <v>45404.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="57" t="s">
         <v>775</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="57">
         <v>34</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="57">
         <v>9</v>
       </c>
-      <c r="D13" s="91">
+      <c r="D13" s="95">
         <f t="shared" si="0"/>
         <v>2.3715277777777776E-2</v>
       </c>
-      <c r="E13" s="45"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="E13" s="45">
+        <v>2</v>
+      </c>
+      <c r="G13" s="97">
+        <v>45405.379166666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="63" t="s">
         <v>776</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="57">
         <v>46</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="57">
         <v>49</v>
       </c>
-      <c r="D14" s="91">
+      <c r="D14" s="95">
         <f t="shared" si="0"/>
         <v>3.2511574074074075E-2</v>
       </c>
-      <c r="E14" s="45"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="E14" s="45">
+        <v>3</v>
+      </c>
+      <c r="G14" s="97">
+        <v>45405.421527777777</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="57" t="s">
         <v>777</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="57">
         <v>41</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="57">
         <v>11</v>
       </c>
-      <c r="D15" s="91">
+      <c r="D15" s="95">
         <f t="shared" si="0"/>
         <v>2.8599537037037038E-2</v>
       </c>
-      <c r="E15" s="45"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="E15" s="45">
+        <v>3</v>
+      </c>
+      <c r="G15" s="97">
+        <v>45405.581944444442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="63" t="s">
         <v>778</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="57">
         <v>50</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="57">
         <v>4</v>
       </c>
-      <c r="D16" s="91">
+      <c r="D16" s="95">
         <f t="shared" si="0"/>
         <v>3.4768518518518518E-2</v>
       </c>
-      <c r="E16" s="45"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="E16" s="45">
+        <v>3</v>
+      </c>
+      <c r="F16" s="90"/>
+      <c r="G16" s="97">
+        <v>45405.662499999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="57" t="s">
         <v>779</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="57">
         <v>34</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="57">
         <v>20</v>
       </c>
-      <c r="D17" s="91">
+      <c r="D17" s="95">
         <f t="shared" si="0"/>
         <v>2.3842592592592592E-2</v>
       </c>
-      <c r="E17" s="45"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="E17" s="45">
+        <v>3</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G17" s="97">
+        <v>45405.933333333334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="63" t="s">
         <v>780</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="57">
         <v>32</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="57">
         <v>57</v>
       </c>
-      <c r="D18" s="91">
+      <c r="D18" s="95">
         <f t="shared" si="0"/>
         <v>2.2881944444444444E-2</v>
       </c>
-      <c r="E18" s="45"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="E18" s="45">
+        <v>4</v>
+      </c>
+      <c r="G18" s="97">
+        <v>45406.463194444441</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="63" t="s">
         <v>781</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="57">
         <v>54</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="57">
         <v>37</v>
       </c>
-      <c r="D19" s="91">
+      <c r="D19" s="95">
         <f t="shared" si="0"/>
         <v>3.7928240740740742E-2</v>
       </c>
-      <c r="E19" s="45"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="E19" s="45">
+        <v>4</v>
+      </c>
+      <c r="G19" s="97">
+        <v>45406.555555555555</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="57" t="s">
         <v>782</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="57">
         <v>33</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="57">
         <v>21</v>
       </c>
-      <c r="D20" s="91">
+      <c r="D20" s="95">
         <f t="shared" si="0"/>
         <v>2.315972222222222E-2</v>
       </c>
-      <c r="E20" s="45"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="E20" s="45">
+        <v>4</v>
+      </c>
+      <c r="G20" s="97">
+        <v>45407.432638888888</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="63" t="s">
         <v>783</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="57">
         <v>30</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="57">
         <v>24</v>
       </c>
-      <c r="D21" s="91">
+      <c r="D21" s="95">
         <f t="shared" si="0"/>
         <v>2.1111111111111108E-2</v>
       </c>
-      <c r="E21" s="45"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="E21" s="45">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1220</v>
+      </c>
+      <c r="G21" s="97">
+        <v>45407.474999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="57" t="s">
         <v>784</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="57">
         <v>31</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="57">
         <v>48</v>
       </c>
-      <c r="D22" s="91">
+      <c r="D22" s="95">
         <f t="shared" si="0"/>
         <v>2.2083333333333333E-2</v>
       </c>
-      <c r="E22" s="45"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="E22" s="45">
+        <v>5</v>
+      </c>
+      <c r="G22" s="97">
+        <v>45407.572222222225</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="57" t="s">
         <v>785</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="57">
         <v>40</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="57">
         <v>3</v>
       </c>
-      <c r="D23" s="91">
+      <c r="D23" s="95">
         <f t="shared" si="0"/>
         <v>2.7812499999999997E-2</v>
       </c>
-      <c r="E23" s="45"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="E23" s="45" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G23" s="97">
+        <v>45448.629166666666</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="57" t="s">
         <v>786</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="57">
         <v>43</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="57">
         <v>26</v>
       </c>
-      <c r="D24" s="91">
+      <c r="D24" s="95">
         <f t="shared" si="0"/>
         <v>3.0162037037037039E-2</v>
       </c>
-      <c r="E24" s="45"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="E24" s="45" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G24" s="97">
+        <v>45408.455555555556</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="63" t="s">
         <v>787</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="57">
         <v>33</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="57">
         <v>10</v>
       </c>
-      <c r="D25" s="91">
+      <c r="D25" s="95">
         <f t="shared" si="0"/>
         <v>2.3032407407407404E-2</v>
       </c>
-      <c r="E25" s="45"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="E25" s="45">
+        <v>7</v>
+      </c>
+      <c r="G25" s="97">
+        <v>45408.604861111111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="57" t="s">
         <v>788</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="57">
         <v>33</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="57">
         <v>37</v>
       </c>
-      <c r="D26" s="91">
+      <c r="D26" s="95">
         <f t="shared" si="0"/>
         <v>2.3344907407407404E-2</v>
       </c>
-      <c r="E26" s="45"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="E26" s="45">
+        <v>7</v>
+      </c>
+      <c r="G26" s="97">
+        <v>45409.396527777775</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="63" t="s">
         <v>789</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="57">
         <v>42</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="57">
         <v>44</v>
       </c>
-      <c r="D27" s="91">
+      <c r="D27" s="95">
         <f t="shared" si="0"/>
         <v>2.9675925925925925E-2</v>
       </c>
-      <c r="E27" s="45"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="E27" s="45">
+        <v>7</v>
+      </c>
+      <c r="G27" s="97">
+        <v>45409.893750000003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="57" t="s">
         <v>790</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="57">
         <v>24</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="57">
         <v>28</v>
       </c>
-      <c r="D28" s="91">
+      <c r="D28" s="95">
         <f t="shared" si="0"/>
         <v>1.699074074074074E-2</v>
       </c>
-      <c r="E28" s="45"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="E28" s="45" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G28" s="97">
+        <v>45449.672222222223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="57" t="s">
         <v>791</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="57">
         <v>35</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="57">
         <v>42</v>
       </c>
-      <c r="D29" s="91">
+      <c r="D29" s="95">
         <f t="shared" si="0"/>
         <v>2.4791666666666667E-2</v>
       </c>
-      <c r="E29" s="45"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="E29" s="45" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G29" s="97">
+        <v>45410.359722222223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="63" t="s">
         <v>792</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="63">
         <v>43</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="63">
         <v>52</v>
       </c>
-      <c r="D30" s="91">
+      <c r="D30" s="95">
         <f t="shared" si="0"/>
         <v>3.0462962962962966E-2</v>
       </c>
-      <c r="E30" s="45"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="E30" s="45" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G30" s="97">
+        <v>45452.272916666669</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="63" t="s">
         <v>793</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="63">
         <v>48</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="63">
         <v>6</v>
       </c>
-      <c r="D31" s="91">
+      <c r="D31" s="95">
         <f t="shared" si="0"/>
         <v>3.3402777777777774E-2</v>
       </c>
-      <c r="E31" s="45"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="E31" s="45">
+        <v>9</v>
+      </c>
+      <c r="G31" s="97">
+        <v>45452.367361111108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="63" t="s">
         <v>794</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="63">
         <v>30</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="63">
         <v>9</v>
       </c>
-      <c r="D32" s="91">
+      <c r="D32" s="95">
         <f t="shared" si="0"/>
         <v>2.0937499999999998E-2</v>
       </c>
-      <c r="E32" s="45"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="E32" s="45">
+        <v>10</v>
+      </c>
+      <c r="G32" s="97">
+        <v>45439.628472222219</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="63" t="s">
         <v>795</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="63">
         <v>26</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="63">
         <v>27</v>
       </c>
-      <c r="D33" s="91">
+      <c r="D33" s="95">
         <f t="shared" si="0"/>
         <v>1.8368055555555554E-2</v>
       </c>
-      <c r="E33" s="45"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="E33" s="45">
+        <v>10</v>
+      </c>
+      <c r="G33" s="97">
+        <v>45452.948611111111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="63" t="s">
         <v>796</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="63">
         <v>39</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="63">
         <v>54</v>
       </c>
-      <c r="D34" s="91">
+      <c r="D34" s="95">
         <f t="shared" si="0"/>
         <v>2.7708333333333335E-2</v>
       </c>
-      <c r="E34" s="45"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+      <c r="E34" s="45" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G34" s="97">
+        <v>45453.760416666664</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="63" t="s">
         <v>797</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="57">
         <v>62</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="57">
         <v>43</v>
       </c>
-      <c r="D35" s="91">
-        <f t="shared" ref="D35:D66" si="1">B35/1440+C35/86400</f>
+      <c r="D35" s="95">
+        <f t="shared" si="0"/>
         <v>4.355324074074074E-2</v>
       </c>
-      <c r="E35" s="45"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E35" s="45" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G35" s="97">
+        <v>45453.861805555556</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
         <v>798</v>
       </c>
-      <c r="D36" s="93">
-        <f>SUM(D6:D35)</f>
-        <v>0.7979166666666665</v>
+      <c r="C36" s="93">
+        <f>SUM(D37:D58)</f>
+        <v>0.65162037037037013</v>
       </c>
       <c r="E36" s="45"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="63" t="s">
         <v>799</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="57">
         <v>18</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="57">
         <v>22</v>
       </c>
-      <c r="D37" s="91">
-        <f t="shared" si="1"/>
+      <c r="D37" s="95">
+        <f t="shared" si="0"/>
         <v>1.275462962962963E-2</v>
       </c>
-      <c r="E37" s="45"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="E37" s="45">
+        <v>13</v>
+      </c>
+      <c r="G37" s="97">
+        <v>45433.911805555559</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="57" t="s">
         <v>800</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="57">
         <v>87</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="57">
         <v>40</v>
       </c>
-      <c r="D38" s="91">
-        <f t="shared" si="1"/>
+      <c r="D38" s="95">
+        <f t="shared" si="0"/>
         <v>6.0879629629629631E-2</v>
       </c>
-      <c r="E38" s="45"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+      <c r="E38" s="45">
+        <v>13</v>
+      </c>
+      <c r="G38" s="97">
+        <v>45421.581944444442</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="57" t="s">
         <v>801</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="57">
         <v>59</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="57">
         <v>4</v>
       </c>
-      <c r="D39" s="91">
-        <f t="shared" si="1"/>
+      <c r="D39" s="95">
+        <f t="shared" si="0"/>
         <v>4.1018518518518517E-2</v>
       </c>
-      <c r="E39" s="45"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+      <c r="E39" s="45">
+        <v>13</v>
+      </c>
+      <c r="G39" s="97">
+        <v>45422.586111111108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="63" t="s">
         <v>802</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="57">
         <v>24</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="57">
         <v>5</v>
       </c>
-      <c r="D40" s="91">
-        <f t="shared" si="1"/>
+      <c r="D40" s="95">
+        <f t="shared" si="0"/>
         <v>1.6724537037037038E-2</v>
       </c>
-      <c r="E40" s="45"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="E40" s="45">
+        <v>14</v>
+      </c>
+      <c r="G40" s="97">
+        <v>45432.881944444445</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="57" t="s">
         <v>803</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="57">
         <v>59</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="57">
         <v>53</v>
       </c>
-      <c r="D41" s="91">
-        <f t="shared" si="1"/>
+      <c r="D41" s="95">
+        <f t="shared" si="0"/>
         <v>4.1585648148148149E-2</v>
       </c>
-      <c r="E41" s="45"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
+      <c r="E41" s="45" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G41" s="97">
+        <v>45434.326388888891</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="57" t="s">
         <v>804</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="57">
         <v>52</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="57">
         <v>12</v>
       </c>
-      <c r="D42" s="91">
-        <f t="shared" si="1"/>
+      <c r="D42" s="95">
+        <f t="shared" si="0"/>
         <v>3.6249999999999998E-2</v>
       </c>
-      <c r="E42" s="45"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="E42" s="45" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G42" s="97">
+        <v>45434.534722222219</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="63" t="s">
         <v>805</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="57">
         <v>53</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="57">
         <v>11</v>
       </c>
-      <c r="D43" s="91">
-        <f t="shared" si="1"/>
+      <c r="D43" s="95">
+        <f t="shared" si="0"/>
         <v>3.6932870370370373E-2</v>
       </c>
-      <c r="E43" s="45"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="E43" s="45">
+        <v>16</v>
+      </c>
+      <c r="G43" s="97">
+        <v>45435.498611111114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="63" t="s">
         <v>806</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="57">
         <v>40</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="57">
         <v>55</v>
       </c>
-      <c r="D44" s="91">
-        <f t="shared" si="1"/>
+      <c r="D44" s="95">
+        <f t="shared" si="0"/>
         <v>2.841435185185185E-2</v>
       </c>
-      <c r="E44" s="45"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+      <c r="E44" s="45">
+        <v>16</v>
+      </c>
+      <c r="G44" s="97">
+        <v>45436.490972222222</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="63" t="s">
         <v>807</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="57">
         <v>55</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="57">
         <v>6</v>
       </c>
-      <c r="D45" s="91">
-        <f t="shared" si="1"/>
+      <c r="D45" s="95">
+        <f t="shared" si="0"/>
         <v>3.8263888888888889E-2</v>
       </c>
-      <c r="E45" s="45"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="E45" s="45">
+        <v>16</v>
+      </c>
+      <c r="G45" s="98">
+        <v>45445.297222222223</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="63" t="s">
         <v>808</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="57">
         <v>44</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="57">
         <v>32</v>
       </c>
-      <c r="D46" s="91">
-        <f t="shared" si="1"/>
+      <c r="D46" s="95">
+        <f t="shared" si="0"/>
         <v>3.0925925925925926E-2</v>
       </c>
-      <c r="E46" s="45"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+      <c r="E46" s="45">
+        <v>17</v>
+      </c>
+      <c r="G46" s="98">
+        <v>45446.452777777777</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="57" t="s">
         <v>809</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="57">
         <v>50</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="57">
         <v>42</v>
       </c>
-      <c r="D47" s="91">
-        <f t="shared" si="1"/>
+      <c r="D47" s="95">
+        <f t="shared" si="0"/>
         <v>3.5208333333333335E-2</v>
       </c>
-      <c r="E47" s="45"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+      <c r="E47" s="45">
+        <v>18</v>
+      </c>
+      <c r="G47" s="98">
+        <v>45446.537499999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="57" t="s">
         <v>810</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="57">
         <v>49</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="57">
         <v>2</v>
       </c>
-      <c r="D48" s="91">
-        <f t="shared" si="1"/>
+      <c r="D48" s="95">
+        <f t="shared" si="0"/>
         <v>3.4050925925925922E-2</v>
       </c>
-      <c r="E48" s="45"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="E48" s="45">
+        <v>18</v>
+      </c>
+      <c r="G48" s="98">
+        <v>45446.591666666667</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="57" t="s">
         <v>811</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="57">
         <v>26</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="57">
         <v>38</v>
       </c>
-      <c r="D49" s="91">
-        <f t="shared" si="1"/>
+      <c r="D49" s="95">
+        <f t="shared" si="0"/>
         <v>1.849537037037037E-2</v>
       </c>
-      <c r="E49" s="45"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+      <c r="E49" s="45">
+        <v>19</v>
+      </c>
+      <c r="G49" s="98">
+        <v>45446.90902777778</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="63" t="s">
         <v>812</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="57">
         <v>25</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="57">
         <v>1</v>
       </c>
-      <c r="D50" s="91">
-        <f t="shared" si="1"/>
+      <c r="D50" s="95">
+        <f t="shared" si="0"/>
         <v>1.7372685185185185E-2</v>
       </c>
-      <c r="E50" s="45"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+      <c r="E50" s="45">
+        <v>19</v>
+      </c>
+      <c r="G50" s="98">
+        <v>45446.938194444447</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="57" t="s">
         <v>813</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="57">
         <v>18</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="57">
         <v>13</v>
       </c>
-      <c r="D51" s="91">
-        <f t="shared" si="1"/>
+      <c r="D51" s="95">
+        <f t="shared" si="0"/>
         <v>1.2650462962962964E-2</v>
       </c>
-      <c r="E51" s="45"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="E51" s="45">
+        <v>19</v>
+      </c>
+      <c r="G51" s="97">
+        <v>45439.459027777775</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="63" t="s">
         <v>814</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="57">
         <v>32</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="57">
         <v>5</v>
       </c>
-      <c r="D52" s="91">
-        <f t="shared" si="1"/>
+      <c r="D52" s="95">
+        <f t="shared" si="0"/>
         <v>2.2280092592592594E-2</v>
       </c>
-      <c r="E52" s="45"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+      <c r="E52" s="45" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G52" s="97">
+        <v>45435.586111111108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="57" t="s">
         <v>815</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="57">
         <v>36</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="57">
         <v>58</v>
       </c>
-      <c r="D53" s="91">
-        <f t="shared" si="1"/>
+      <c r="D53" s="95">
+        <f t="shared" si="0"/>
         <v>2.5671296296296296E-2</v>
       </c>
-      <c r="E53" s="45"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+      <c r="E53" s="45" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G53" s="97">
+        <v>45439.522916666669</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="57" t="s">
         <v>816</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="57">
         <v>62</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="57">
         <v>44</v>
       </c>
-      <c r="D54" s="91">
-        <f t="shared" si="1"/>
+      <c r="D54" s="95">
+        <f t="shared" si="0"/>
         <v>4.3564814814814813E-2</v>
       </c>
-      <c r="E54" s="45"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="E54" s="45" t="s">
+        <v>1226</v>
+      </c>
+      <c r="G54" s="97">
+        <v>45435.910416666666</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="57" t="s">
         <v>817</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="57">
         <v>38</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="57">
         <v>17</v>
       </c>
-      <c r="D55" s="91">
-        <f t="shared" si="1"/>
+      <c r="D55" s="95">
+        <f t="shared" si="0"/>
         <v>2.6585648148148146E-2</v>
       </c>
-      <c r="E55" s="45"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+      <c r="E55" s="45">
+        <v>20</v>
+      </c>
+      <c r="G55" s="97">
+        <v>45440.898611111108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="57" t="s">
         <v>818</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="57">
         <v>25</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="57">
         <v>47</v>
       </c>
-      <c r="D56" s="91">
-        <f t="shared" si="1"/>
+      <c r="D56" s="95">
+        <f t="shared" si="0"/>
         <v>1.7905092592592594E-2</v>
       </c>
-      <c r="E56" s="45"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="E56" s="45" t="s">
+        <v>1227</v>
+      </c>
+      <c r="G56" s="97">
+        <v>45441.93472222222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="57">
         <v>33</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="57">
         <v>17</v>
       </c>
-      <c r="D57" s="91">
-        <f t="shared" si="1"/>
+      <c r="D57" s="95">
+        <f t="shared" si="0"/>
         <v>2.3113425925925923E-2</v>
       </c>
-      <c r="E57" s="45"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+      <c r="E57" s="45">
+        <v>21</v>
+      </c>
+      <c r="G57" s="97">
+        <v>45444.939583333333</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="57" t="s">
         <v>820</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="57">
         <v>44</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="57">
         <v>36</v>
       </c>
-      <c r="D58" s="91">
-        <f t="shared" si="1"/>
+      <c r="D58" s="95">
+        <f t="shared" si="0"/>
         <v>3.097222222222222E-2</v>
       </c>
-      <c r="E58" s="45"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E58" s="45">
+        <v>21</v>
+      </c>
+      <c r="G58" s="97">
+        <v>45439.416666666664</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="25" t="s">
         <v>821</v>
       </c>
-      <c r="D59" s="93">
-        <f>SUM(D37:D58)</f>
-        <v>0.65162037037037013</v>
+      <c r="C59" s="93">
+        <f>SUM(D60:D102)</f>
+        <v>1.0073379629629633</v>
       </c>
       <c r="E59" s="45"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="57" t="s">
         <v>799</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="57">
         <v>6</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="57">
         <v>9</v>
       </c>
-      <c r="D60" s="91">
-        <f t="shared" si="1"/>
+      <c r="D60" s="95">
+        <f t="shared" si="0"/>
         <v>4.2708333333333331E-3</v>
       </c>
-      <c r="E60" s="45"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E60" s="45">
+        <v>21</v>
+      </c>
+      <c r="G60" s="99">
+        <v>45502.651388888888</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>822</v>
       </c>
@@ -12474,12 +12863,12 @@
         <v>36</v>
       </c>
       <c r="D61" s="91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2916666666666667E-2</v>
       </c>
       <c r="E61" s="45"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>823</v>
       </c>
@@ -12490,12 +12879,12 @@
         <v>54</v>
       </c>
       <c r="D62" s="91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.2152777777777778E-2</v>
       </c>
       <c r="E62" s="45"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>824</v>
       </c>
@@ -12506,12 +12895,12 @@
         <v>2</v>
       </c>
       <c r="D63" s="91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.7106481481481481E-2</v>
       </c>
       <c r="E63" s="45"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>825</v>
       </c>
@@ -12522,7 +12911,7 @@
         <v>51</v>
       </c>
       <c r="D64" s="91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.6979166666666665E-2</v>
       </c>
       <c r="E64" s="45"/>
@@ -12538,7 +12927,7 @@
         <v>8</v>
       </c>
       <c r="D65" s="91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2.6481481481481481E-2</v>
       </c>
       <c r="E65" s="45"/>
@@ -12554,7 +12943,7 @@
         <v>2</v>
       </c>
       <c r="D66" s="91">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4.5856481481481477E-2</v>
       </c>
       <c r="E66" s="45"/>
@@ -12570,7 +12959,7 @@
         <v>59</v>
       </c>
       <c r="D67" s="91">
-        <f t="shared" ref="D67:D98" si="2">B67/1440+C67/86400</f>
+        <f t="shared" ref="D67:D102" si="1">B67/1440+C67/86400</f>
         <v>1.7349537037037038E-2</v>
       </c>
       <c r="E67" s="45"/>
@@ -12586,7 +12975,7 @@
         <v>44</v>
       </c>
       <c r="D68" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.1620370370370371E-2</v>
       </c>
       <c r="E68" s="45"/>
@@ -12602,7 +12991,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.1817129629629629E-2</v>
       </c>
       <c r="E69" s="45"/>
@@ -12618,7 +13007,7 @@
         <v>36</v>
       </c>
       <c r="D70" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.7083333333333332E-2</v>
       </c>
       <c r="E70" s="45"/>
@@ -12634,7 +13023,7 @@
         <v>34</v>
       </c>
       <c r="D71" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.1921296296296296E-2</v>
       </c>
       <c r="E71" s="45"/>
@@ -12650,7 +13039,7 @@
         <v>59</v>
       </c>
       <c r="D72" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5266203703703704E-2</v>
       </c>
       <c r="E72" s="45"/>
@@ -12666,7 +13055,7 @@
         <v>49</v>
       </c>
       <c r="D73" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.5150462962962963E-2</v>
       </c>
       <c r="E73" s="45"/>
@@ -12682,7 +13071,7 @@
         <v>28</v>
       </c>
       <c r="D74" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4212962962962962E-2</v>
       </c>
       <c r="E74" s="45"/>
@@ -12698,7 +13087,7 @@
         <v>20</v>
       </c>
       <c r="D75" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.0370370370370372E-2</v>
       </c>
       <c r="E75" s="45"/>
@@ -12714,7 +13103,7 @@
         <v>16</v>
       </c>
       <c r="D76" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.2546296296296297E-2</v>
       </c>
       <c r="E76" s="45"/>
@@ -12730,7 +13119,7 @@
         <v>17</v>
       </c>
       <c r="D77" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4780092592592593E-2</v>
       </c>
       <c r="E77" s="45"/>
@@ -12746,7 +13135,7 @@
         <v>35</v>
       </c>
       <c r="D78" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.3599537037037037E-2</v>
       </c>
       <c r="E78" s="45"/>
@@ -12762,7 +13151,7 @@
         <v>42</v>
       </c>
       <c r="D79" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.7708333333333332E-2</v>
       </c>
       <c r="E79" s="45"/>
@@ -12778,7 +13167,7 @@
         <v>36</v>
       </c>
       <c r="D80" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.4444444444444444E-2</v>
       </c>
       <c r="E80" s="45"/>
@@ -12794,7 +13183,7 @@
         <v>12</v>
       </c>
       <c r="D81" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.027777777777778E-2</v>
       </c>
       <c r="E81" s="45"/>
@@ -12810,7 +13199,7 @@
         <v>24</v>
       </c>
       <c r="D82" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.9861111111111111E-2</v>
       </c>
       <c r="E82" s="45"/>
@@ -12826,7 +13215,7 @@
         <v>33</v>
       </c>
       <c r="D83" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4270833333333333E-2</v>
       </c>
       <c r="E83" s="45"/>
@@ -12842,7 +13231,7 @@
         <v>23</v>
       </c>
       <c r="D84" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.9849537037037037E-2</v>
       </c>
       <c r="E84" s="45"/>
@@ -12858,7 +13247,7 @@
         <v>53</v>
       </c>
       <c r="D85" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.1585648148148149E-2</v>
       </c>
       <c r="E85" s="45"/>
@@ -12874,7 +13263,7 @@
         <v>52</v>
       </c>
       <c r="D86" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.740740740740741E-2</v>
       </c>
       <c r="E86" s="45"/>
@@ -12890,7 +13279,7 @@
         <v>7</v>
       </c>
       <c r="D87" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.0914351851851851E-2</v>
       </c>
       <c r="E87" s="45"/>
@@ -12906,7 +13295,7 @@
         <v>21</v>
       </c>
       <c r="D88" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.1354166666666667E-2</v>
       </c>
       <c r="E88" s="45"/>
@@ -12922,7 +13311,7 @@
         <v>32</v>
       </c>
       <c r="D89" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.1481481481481481E-2</v>
       </c>
       <c r="E89" s="45"/>
@@ -12938,7 +13327,7 @@
         <v>51</v>
       </c>
       <c r="D90" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.8090277777777778E-2</v>
       </c>
       <c r="E90" s="45"/>
@@ -12954,7 +13343,7 @@
         <v>54</v>
       </c>
       <c r="D91" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.6597222222222222E-2</v>
       </c>
       <c r="E91" s="45"/>
@@ -12970,7 +13359,7 @@
         <v>6</v>
       </c>
       <c r="D92" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.0624999999999999E-2</v>
       </c>
       <c r="E92" s="45"/>
@@ -12986,7 +13375,7 @@
         <v>30</v>
       </c>
       <c r="D93" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.8402777777777775E-2</v>
       </c>
       <c r="E93" s="45"/>
@@ -13002,7 +13391,7 @@
         <v>17</v>
       </c>
       <c r="D94" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>4.4641203703703704E-2</v>
       </c>
       <c r="E94" s="45"/>
@@ -13018,7 +13407,7 @@
         <v>22</v>
       </c>
       <c r="D95" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.8310185185185183E-2</v>
       </c>
       <c r="E95" s="45"/>
@@ -13034,7 +13423,7 @@
         <v>10</v>
       </c>
       <c r="D96" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.0671296296296294E-2</v>
       </c>
       <c r="E96" s="45"/>
@@ -13050,7 +13439,7 @@
         <v>43</v>
       </c>
       <c r="D97" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.1331018518518517E-2</v>
       </c>
       <c r="E97" s="45"/>
@@ -13066,7 +13455,7 @@
         <v>16</v>
       </c>
       <c r="D98" s="91">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.2129629629629626E-2</v>
       </c>
       <c r="E98" s="45"/>
@@ -13082,7 +13471,7 @@
         <v>24</v>
       </c>
       <c r="D99" s="91">
-        <f t="shared" ref="D99:D102" si="3">B99/1440+C99/86400</f>
+        <f t="shared" si="1"/>
         <v>1.5555555555555555E-2</v>
       </c>
       <c r="E99" s="45"/>
@@ -13098,7 +13487,7 @@
         <v>42</v>
       </c>
       <c r="D100" s="91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2.4097222222222221E-2</v>
       </c>
       <c r="E100" s="45"/>
@@ -13114,7 +13503,7 @@
         <v>30</v>
       </c>
       <c r="D101" s="91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1.2847222222222223E-2</v>
       </c>
       <c r="E101" s="45"/>
@@ -13130,7 +13519,7 @@
         <v>54</v>
       </c>
       <c r="D102" s="91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>3.402777777777778E-3</v>
       </c>
       <c r="E102" s="45"/>
@@ -13138,16 +13527,43 @@
     <row r="103" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A103" s="11" t="str">
         <f>"总时长："&amp;TEXT(SUM(B:B)/1440+SUM(C:C)/86400,"[h]:mm:ss")</f>
-        <v>总时长：59:26:28</v>
-      </c>
-      <c r="D103" s="93">
-        <f>SUM(D60:D102)</f>
-        <v>1.0073379629629633</v>
+        <v>总时长：59:26:30</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="D60:D102">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8275B0C3-DF87-4C89-9CAC-283E048F50B2}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8275B0C3-DF87-4C89-9CAC-283E048F50B2}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D60:D102</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -18432,6 +18848,198 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CEFC2E3-EED2-454A-8E0C-28D2F8839966}">
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="79" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B2">
+        <v>24</v>
+      </c>
+      <c r="C2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B4">
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B6">
+        <v>27</v>
+      </c>
+      <c r="C6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B7">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B9">
+        <v>19</v>
+      </c>
+      <c r="C9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B11">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B13">
+        <v>13</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B14">
+        <v>26</v>
+      </c>
+      <c r="C14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="58" t="str">
+        <f>"总时长："&amp;TEXT(SUM(B:B)/1440+SUM(C:C)/86400,"[h]:mm:ss")</f>
+        <v>总时长：5:30:46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
